--- a/news_daily/2026-08-21.xlsx
+++ b/news_daily/2026-08-21.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -101,9 +96,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH24"/>
+  <dimension ref="A1:BL24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -1007,6 +1023,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1177,176 +1197,208 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Automatic Data Processing, Inc.</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2026-08-21T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Fantasy Football ADP: Exploiting Default Rankings for 2026</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0.032</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNZ0VpOXBNeW51MDZ4ZjlwMFhZZU1xTVlxczBhVmI0UVc4VjRkQTZ6RktTSEtIbFNTeFBqQWJja0xFNVh2a1ljMk11dkVYV3R0S3VzVFhmV2tMUFBPLUJQeElFZThmOWlGZkNHRVBEb19IbnBQYUhmSUpLTkd2djBadV8tMzFkM1FyMlFjc1lkX00wckFsYlgtZ3NJRV9aby1DaHpwV2Q5RXlPaG81elE4?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>RotoWire</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>9ce40a2e73e44ce1a35e8f45dc851c23</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>b2c1a94eaab81f88a6c05a9c</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr">
+        <is>
+          <t>6b8fda4a1b3b10248ded95ba</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AK4" s="2" t="inlineStr"/>
+      <c r="AL4" s="2" t="inlineStr"/>
+      <c r="AM4" s="2" t="inlineStr"/>
+      <c r="AN4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>0.032</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNZ0VpOXBNeW51MDZ4ZjlwMFhZZU1xTVlxczBhVmI0UVc4VjRkQTZ6RktTSEtIbFNTeFBqQWJja0xFNVh2a1ljMk11dkVYV3R0S3VzVFhmV2tMUFBPLUJQeElFZThmOWlGZkNHRVBEb19IbnBQYUhmSUpLTkd2djBadV8tMzFkM1FyMlFjc1lkX00wckFsYlgtZ3NJRV9aby1DaHpwV2Q5RXlPaG81elE4?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>RotoWire</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>b2c1a94eaab81f88a6c05a9c</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>6b8fda4a1b3b10248ded95ba</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr"/>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr">
+      <c r="AP4" s="2" t="inlineStr"/>
+      <c r="AQ4" s="2" t="inlineStr"/>
+      <c r="AR4" s="2" t="inlineStr"/>
+      <c r="AS4" s="2" t="inlineStr"/>
+      <c r="AT4" s="2" t="inlineStr"/>
+      <c r="AU4" s="2" t="inlineStr"/>
+      <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr">
+      <c r="AX4" s="2" t="inlineStr"/>
+      <c r="AY4" s="2" t="inlineStr"/>
+      <c r="AZ4" s="2" t="inlineStr"/>
+      <c r="BA4" s="2" t="inlineStr"/>
+      <c r="BB4" s="2" t="inlineStr">
         <is>
           <t>ADP</t>
         </is>
       </c>
-      <c r="BC4" s="3" t="inlineStr">
+      <c r="BC4" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="3" t="inlineStr"/>
-      <c r="BE4" s="3" t="inlineStr">
+      <c r="BD4" s="2" t="inlineStr"/>
+      <c r="BE4" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF4" s="3" t="inlineStr">
+      <c r="BF4" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG4" s="3" t="inlineStr">
+      <c r="BG4" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1517,508 +1569,564 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>BAC</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Bank of America Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2026-08-21T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>SEC charges former Bank of America investment banker with insider trading</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>內線交易</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>'-0.722</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOMU4yOXN1ZWhTdkplbWUwX2xldjh1TWxjN3NCOUhJNjdzR1JKYzZZeGR4SHdjc1Q5elpCUFJQdXFwMmtyZ29jMTFnUXFxTExpSGZ6TUtZT3BCZEtaQXZkbFRhMTFrNGtqUlVobWZVSjltQXhfZHdERzlwNXlfS3F5WENBRUsxc3l0QmRFR0J5VmItVDdnOHpkVV9ESUEzMUpfRVlnOFA1b0NmeER3SWhPaXcyM3N5YzAzVDdoRzRKWkw?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>GOVERNANCE</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>INSIDER_TRADING</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>insider trading</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>df0a320ae25f4a5da149a50349a707ca</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>3a4ca9a95155b8245d865ddc</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>cb26369e7afea25be8d4a326</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>'-0.722</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOMU4yOXN1ZWhTdkplbWUwX2xldjh1TWxjN3NCOUhJNjdzR1JKYzZZeGR4SHdjc1Q5elpCUFJQdXFwMmtyZ29jMTFnUXFxTExpSGZ6TUtZT3BCZEtaQXZkbFRhMTFrNGtqUlVobWZVSjltQXhfZHdERzlwNXlfS3F5WENBRUsxc3l0QmRFR0J5VmItVDdnOHpkVV9ESUEzMUpfRVlnOFA1b0NmeER3SWhPaXcyM3N5YzAzVDdoRzRKWkw?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>GOVERNANCE</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>INSIDER_TRADING</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>insider trading</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>3a4ca9a95155b8245d865ddc</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>cb26369e7afea25be8d4a326</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
         <is>
           <t>BAC</t>
         </is>
       </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="4" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="4" t="inlineStr">
+      <c r="BG6" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Equifax, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>2026-08-21T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Equifax agrees to $100M deal to end class action claims over credit score error</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOV0tZQUdjZmhXS3k3YmU1UWFEY2NRWEJWQzRrekhxdFcwZTNicF84TzdiMTRVdnRZSEZyY0UxTzJMazhVRUdPTUhmRU0tR3ZpUjFqWk9vZmhjMXlSdFVkdmIxNGVaa3BqSWVDWGJFRTZaekFkZTk0M0QtUzRCUFhaMVBlWUFXZENSUFRIQkZZbVFtN3lVWFY1S1ktZlZMaF82LW1Oa0tWM0xpTGJUZzVValRpZjAyekZtVmRHVzVCdWRRQmJBZ1BPcFFKTEV3RldGdVI1ZXlmQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Top Class Actions</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr"/>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>2e1eb4eaea9f470b874805250104f5d4</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>a93ac553e37f4eeb8a503b0e</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>ec8e6b1a1b1c66ac1d45db71</t>
+        </is>
+      </c>
+      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AF7" s="3" t="inlineStr"/>
+      <c r="AG7" s="3" t="inlineStr"/>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr"/>
+      <c r="AM7" s="3" t="inlineStr"/>
+      <c r="AN7" s="3" t="inlineStr"/>
+      <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr"/>
-      <c r="R7" s="4" t="inlineStr"/>
-      <c r="S7" s="4" t="inlineStr"/>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOV0tZQUdjZmhXS3k3YmU1UWFEY2NRWEJWQzRrekhxdFcwZTNicF84TzdiMTRVdnRZSEZyY0UxTzJMazhVRUdPTUhmRU0tR3ZpUjFqWk9vZmhjMXlSdFVkdmIxNGVaa3BqSWVDWGJFRTZaekFkZTk0M0QtUzRCUFhaMVBlWUFXZENSUFRIQkZZbVFtN3lVWFY1S1ktZlZMaF82LW1Oa0tWM0xpTGJUZzVValRpZjAyekZtVmRHVzVCdWRRQmJBZ1BPcFFKTEV3RldGdVI1ZXlmQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="4" t="inlineStr">
-        <is>
-          <t>Top Class Actions</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="inlineStr"/>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z7" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="inlineStr"/>
-      <c r="AB7" s="4" t="inlineStr"/>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>a93ac553e37f4eeb8a503b0e</t>
-        </is>
-      </c>
-      <c r="AD7" s="4" t="inlineStr">
-        <is>
-          <t>ec8e6b1a1b1c66ac1d45db71</t>
-        </is>
-      </c>
-      <c r="AE7" s="4" t="inlineStr"/>
-      <c r="AF7" s="4" t="inlineStr"/>
-      <c r="AG7" s="4" t="inlineStr"/>
-      <c r="AH7" s="4" t="inlineStr"/>
-      <c r="AI7" s="4" t="inlineStr"/>
-      <c r="AJ7" s="4" t="inlineStr"/>
-      <c r="AK7" s="4" t="inlineStr"/>
-      <c r="AL7" s="4" t="inlineStr"/>
-      <c r="AM7" s="4" t="inlineStr"/>
-      <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
-      <c r="AP7" s="4" t="inlineStr"/>
-      <c r="AQ7" s="4" t="inlineStr"/>
-      <c r="AR7" s="4" t="inlineStr"/>
-      <c r="AS7" s="4" t="inlineStr"/>
-      <c r="AT7" s="4" t="inlineStr"/>
-      <c r="AU7" s="4" t="inlineStr"/>
-      <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr">
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr"/>
+      <c r="AS7" s="3" t="inlineStr"/>
+      <c r="AT7" s="3" t="inlineStr"/>
+      <c r="AU7" s="3" t="inlineStr"/>
+      <c r="AV7" s="3" t="inlineStr"/>
+      <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX7" s="4" t="inlineStr"/>
-      <c r="AY7" s="4" t="inlineStr"/>
-      <c r="AZ7" s="4" t="inlineStr"/>
-      <c r="BA7" s="4" t="inlineStr"/>
-      <c r="BB7" s="4" t="inlineStr">
+      <c r="AX7" s="3" t="inlineStr"/>
+      <c r="AY7" s="3" t="inlineStr"/>
+      <c r="AZ7" s="3" t="inlineStr"/>
+      <c r="BA7" s="3" t="inlineStr"/>
+      <c r="BB7" s="3" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="BC7" s="4" t="inlineStr">
+      <c r="BC7" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="4" t="inlineStr"/>
-      <c r="BE7" s="4" t="inlineStr">
+      <c r="BD7" s="3" t="inlineStr"/>
+      <c r="BE7" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF7" s="4" t="inlineStr">
+      <c r="BF7" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG7" s="4" t="inlineStr">
+      <c r="BG7" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>CLX</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Clorox</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>2026-08-21T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Is Clorox Stock Worth Buying as GOJO Growth Meets Margin Pressure?</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>營運惡化</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr"/>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>0.213</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr"/>
-      <c r="Q8" s="5" t="inlineStr"/>
-      <c r="R8" s="5" t="inlineStr"/>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U8" s="5" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORDA1M0V5STZJYnZjTzdCSVdPQkhvSS1qa0J5VThsVkFHbnNUaUdScFUtQmZLSkxJT0VSS2loLTZ1QVVaUjM4VkRqRjJicTk1b3BjeFBVZFE4QVE1bDZObTJZQm40Y2NyQW9XYXhNdnRRMXd1dUNJS05Yak5JdkVHS3BYdXVYNHFyMGtkM1doQ1dPclhQT1VZbTV6Zw?oc=5</t>
         </is>
       </c>
-      <c r="V8" s="5" t="inlineStr">
+      <c r="V8" s="4" t="inlineStr">
         <is>
           <t>Yahoo Finance</t>
         </is>
       </c>
-      <c r="W8" s="5" t="inlineStr"/>
-      <c r="X8" s="5" t="inlineStr">
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y8" s="5" t="inlineStr">
+      <c r="Y8" s="4" t="inlineStr">
         <is>
           <t>OPERATING_DETERIORATION</t>
         </is>
       </c>
-      <c r="Z8" s="5" t="inlineStr">
+      <c r="Z8" s="4" t="inlineStr">
         <is>
           <t>margin pressure</t>
         </is>
       </c>
-      <c r="AA8" s="5" t="inlineStr"/>
-      <c r="AB8" s="5" t="inlineStr"/>
-      <c r="AC8" s="5" t="inlineStr">
+      <c r="AA8" s="4" t="inlineStr"/>
+      <c r="AB8" s="4" t="inlineStr"/>
+      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>67227f019967c42a43b36773</t>
         </is>
       </c>
-      <c r="AD8" s="5" t="inlineStr">
+      <c r="AD8" s="4" t="inlineStr">
         <is>
           <t>b3bfb07265a165d7e7332a07</t>
         </is>
       </c>
-      <c r="AE8" s="5" t="inlineStr"/>
-      <c r="AF8" s="5" t="inlineStr"/>
-      <c r="AG8" s="5" t="inlineStr"/>
-      <c r="AH8" s="5" t="inlineStr"/>
-      <c r="AI8" s="5" t="inlineStr"/>
-      <c r="AJ8" s="5" t="inlineStr"/>
-      <c r="AK8" s="5" t="inlineStr"/>
-      <c r="AL8" s="5" t="inlineStr"/>
-      <c r="AM8" s="5" t="inlineStr"/>
-      <c r="AN8" s="5" t="inlineStr"/>
-      <c r="AO8" s="5" t="inlineStr"/>
-      <c r="AP8" s="5" t="inlineStr"/>
-      <c r="AQ8" s="5" t="inlineStr"/>
-      <c r="AR8" s="5" t="inlineStr"/>
-      <c r="AS8" s="5" t="inlineStr"/>
-      <c r="AT8" s="5" t="inlineStr"/>
-      <c r="AU8" s="5" t="inlineStr"/>
-      <c r="AV8" s="5" t="inlineStr"/>
-      <c r="AW8" s="5" t="inlineStr"/>
-      <c r="AX8" s="5" t="inlineStr"/>
-      <c r="AY8" s="5" t="inlineStr"/>
-      <c r="AZ8" s="5" t="inlineStr"/>
-      <c r="BA8" s="5" t="inlineStr"/>
-      <c r="BB8" s="5" t="inlineStr">
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr"/>
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr"/>
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
         <is>
           <t>CLX</t>
         </is>
       </c>
-      <c r="BC8" s="5" t="inlineStr">
+      <c r="BC8" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="5" t="inlineStr"/>
-      <c r="BE8" s="5" t="inlineStr">
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF8" s="5" t="inlineStr"/>
-      <c r="BG8" s="5" t="inlineStr">
+      <c r="BF8" s="4" t="inlineStr"/>
+      <c r="BG8" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH8" s="5" t="inlineStr"/>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr"/>
+      <c r="BL8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2189,6 +2297,10 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2359,6 +2471,10 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr"/>
+      <c r="BL10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2529,6 +2645,10 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BJ11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr"/>
+      <c r="BL11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2699,512 +2819,584 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr"/>
+      <c r="BL12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Walt Disney Company (The)</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>2026-08-21T10:55:17+08:00</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>美司法部反對就迪士尼ABC牌照訴訟案舉行緊急聽證會</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2624496</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>7a286744031f4dfb8060d957459d14f1</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>153c67f9d747a4285d681ba3</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr">
+        <is>
+          <t>3659fbbaa3cea9a8a2d4b980</t>
+        </is>
+      </c>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr"/>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr">
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr"/>
+      <c r="AS13" s="3" t="inlineStr"/>
+      <c r="AT13" s="3" t="inlineStr"/>
+      <c r="AU13" s="3" t="inlineStr"/>
+      <c r="AV13" s="3" t="inlineStr"/>
+      <c r="AW13" s="3" t="inlineStr"/>
+      <c r="AX13" s="3" t="inlineStr"/>
+      <c r="AY13" s="3" t="inlineStr"/>
+      <c r="AZ13" s="3" t="inlineStr"/>
+      <c r="BA13" s="3" t="inlineStr"/>
+      <c r="BB13" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="BC13" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2624496</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr"/>
-      <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t>153c67f9d747a4285d681ba3</t>
-        </is>
-      </c>
-      <c r="AD13" s="4" t="inlineStr">
-        <is>
-          <t>3659fbbaa3cea9a8a2d4b980</t>
-        </is>
-      </c>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP13" s="4" t="inlineStr"/>
-      <c r="AQ13" s="4" t="inlineStr"/>
-      <c r="AR13" s="4" t="inlineStr"/>
-      <c r="AS13" s="4" t="inlineStr"/>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr"/>
-      <c r="AX13" s="4" t="inlineStr"/>
-      <c r="AY13" s="4" t="inlineStr"/>
-      <c r="AZ13" s="4" t="inlineStr"/>
-      <c r="BA13" s="4" t="inlineStr"/>
-      <c r="BB13" s="4" t="inlineStr">
+      <c r="BD13" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="BC13" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD13" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BE13" s="4" t="inlineStr">
+      <c r="BE13" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF13" s="4" t="inlineStr">
+      <c r="BF13" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG13" s="4" t="inlineStr"/>
-      <c r="BH13" s="4" t="inlineStr"/>
+      <c r="BG13" s="3" t="inlineStr"/>
+      <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Abbott Laboratories</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>2026-08-21T09:51:53+08:00</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>雅培將支付6.7億美元以了結部分早產兒配方奶粉訴訟</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2624374</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>9e313718274e4982b87c9e28823cbfe4</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>dbea804fa21928a28a097664</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>2c47dcd5fe84634ff135980b</t>
+        </is>
+      </c>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr"/>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr">
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr"/>
+      <c r="AS14" s="3" t="inlineStr"/>
+      <c r="AT14" s="3" t="inlineStr"/>
+      <c r="AU14" s="3" t="inlineStr"/>
+      <c r="AV14" s="3" t="inlineStr"/>
+      <c r="AW14" s="3" t="inlineStr"/>
+      <c r="AX14" s="3" t="inlineStr"/>
+      <c r="AY14" s="3" t="inlineStr"/>
+      <c r="AZ14" s="3" t="inlineStr"/>
+      <c r="BA14" s="3" t="inlineStr"/>
+      <c r="BB14" s="3" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="BC14" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2624374</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr"/>
-      <c r="AB14" s="4" t="inlineStr"/>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>dbea804fa21928a28a097664</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>2c47dcd5fe84634ff135980b</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="inlineStr"/>
-      <c r="AG14" s="4" t="inlineStr"/>
-      <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr"/>
-      <c r="AL14" s="4" t="inlineStr"/>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP14" s="4" t="inlineStr"/>
-      <c r="AQ14" s="4" t="inlineStr"/>
-      <c r="AR14" s="4" t="inlineStr"/>
-      <c r="AS14" s="4" t="inlineStr"/>
-      <c r="AT14" s="4" t="inlineStr"/>
-      <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr"/>
-      <c r="AX14" s="4" t="inlineStr"/>
-      <c r="AY14" s="4" t="inlineStr"/>
-      <c r="AZ14" s="4" t="inlineStr"/>
-      <c r="BA14" s="4" t="inlineStr"/>
-      <c r="BB14" s="4" t="inlineStr">
+      <c r="BD14" s="3" t="inlineStr">
         <is>
           <t>ABT</t>
         </is>
       </c>
-      <c r="BC14" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD14" s="4" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="BE14" s="4" t="inlineStr">
+      <c r="BE14" s="3" t="inlineStr">
         <is>
           <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
         </is>
       </c>
-      <c r="BF14" s="4" t="inlineStr">
+      <c r="BF14" s="3" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="BG14" s="4" t="inlineStr"/>
-      <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BG14" s="3" t="inlineStr"/>
+      <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>AT&amp;T</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-08-21T06:02:16+08:00</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Federal prosecutors take over charges in Rutland murder case, won’t seek death penalty</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQQWU4R0RnaXNHby02QmxXZDVmc0pWdkRZazREQzluNU1PV3YwRVlCX3dGaDJTYWxWY3J2ejl5SzNiaUlHS3B4cFFaSWloWVl0SGJyVjFpRFUtdjNQNGM0S2lQaWl5NW5BUzczNFdxNjRDUWFCRm4zaXZwbnVTaVRiS3YydWpnUVhHemFBbk13RjBhbG1mWTdzbE5DWDNkOThCd3QzUU85R0Exem43RlJFa05VbVYyM04t?oc=5</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>vtdigger.org</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>penalty</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>de17ac4246294c2cb86574fcd2868dc3</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>05ae3052aa091667cf1b0b3c</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>d73878c04251aaaf0ee40892</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="2" t="inlineStr"/>
+      <c r="AM15" s="2" t="inlineStr"/>
+      <c r="AN15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr">
+      <c r="AP15" s="2" t="inlineStr"/>
+      <c r="AQ15" s="2" t="inlineStr"/>
+      <c r="AR15" s="2" t="inlineStr"/>
+      <c r="AS15" s="2" t="inlineStr"/>
+      <c r="AT15" s="2" t="inlineStr"/>
+      <c r="AU15" s="2" t="inlineStr"/>
+      <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" s="2" t="inlineStr"/>
+      <c r="AX15" s="2" t="inlineStr"/>
+      <c r="AY15" s="2" t="inlineStr"/>
+      <c r="AZ15" s="2" t="inlineStr"/>
+      <c r="BA15" s="2" t="inlineStr"/>
+      <c r="BB15" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="BC15" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQQWU4R0RnaXNHby02QmxXZDVmc0pWdkRZazREQzluNU1PV3YwRVlCX3dGaDJTYWxWY3J2ejl5SzNiaUlHS3B4cFFaSWloWVl0SGJyVjFpRFUtdjNQNGM0S2lQaWl5NW5BUzczNFdxNjRDUWFCRm4zaXZwbnVTaVRiS3YydWpnUVhHemFBbk13RjBhbG1mWTdzbE5DWDNkOThCd3QzUU85R0Exem43RlJFa05VbVYyM04t?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>vtdigger.org</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z15" s="4" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="AA15" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="inlineStr">
-        <is>
-          <t>05ae3052aa091667cf1b0b3c</t>
-        </is>
-      </c>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t>d73878c04251aaaf0ee40892</t>
-        </is>
-      </c>
-      <c r="AE15" s="4" t="inlineStr"/>
-      <c r="AF15" s="4" t="inlineStr"/>
-      <c r="AG15" s="4" t="inlineStr"/>
-      <c r="AH15" s="4" t="inlineStr"/>
-      <c r="AI15" s="4" t="inlineStr"/>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="4" t="inlineStr"/>
-      <c r="AL15" s="4" t="inlineStr"/>
-      <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP15" s="4" t="inlineStr"/>
-      <c r="AQ15" s="4" t="inlineStr"/>
-      <c r="AR15" s="4" t="inlineStr"/>
-      <c r="AS15" s="4" t="inlineStr"/>
-      <c r="AT15" s="4" t="inlineStr"/>
-      <c r="AU15" s="4" t="inlineStr"/>
-      <c r="AV15" s="4" t="inlineStr"/>
-      <c r="AW15" s="4" t="inlineStr"/>
-      <c r="AX15" s="4" t="inlineStr"/>
-      <c r="AY15" s="4" t="inlineStr"/>
-      <c r="AZ15" s="4" t="inlineStr"/>
-      <c r="BA15" s="4" t="inlineStr"/>
-      <c r="BB15" s="4" t="inlineStr">
+      <c r="BD15" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="BC15" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD15" s="4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BE15" s="4" t="inlineStr">
+      <c r="BE15" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF15" s="4" t="inlineStr">
+      <c r="BF15" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG15" s="4" t="inlineStr"/>
-      <c r="BH15" s="4" t="inlineStr"/>
+      <c r="BG15" s="2" t="inlineStr"/>
+      <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3379,172 +3571,180 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr"/>
+      <c r="BL16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>APO</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Apollo Global Management</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>2026-08-21T04:19:45+08:00</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Apollo Global Management Data Breach Impacts SSNs; Lawsuit Possible</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>資料外洩</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr"/>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>'-0.933</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr"/>
-      <c r="Q17" s="5" t="inlineStr"/>
-      <c r="R17" s="5" t="inlineStr"/>
-      <c r="S17" s="5" t="inlineStr"/>
-      <c r="T17" s="5" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr"/>
+      <c r="S17" s="4" t="inlineStr"/>
+      <c r="T17" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U17" s="5" t="inlineStr">
+      <c r="U17" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNSGlaMkhFZWFObEtxVWo4MFdxSTBkZFJJWFU3Z3BKamRKa0VqRVBmWV9LY29pSy1YV29icjJwLWppRnVXZEMtMUFabGpRX2NYMGNBeHpvdDBDdFZZa2ZxY1dyaGFqcklCeUx2T09TcUFXWVVEUUltdGhBeDNlSzUteEtBMjFndVgxRllaZkhR?oc=5</t>
         </is>
       </c>
-      <c r="V17" s="5" t="inlineStr">
+      <c r="V17" s="4" t="inlineStr">
         <is>
           <t>classaction.org</t>
         </is>
       </c>
-      <c r="W17" s="5" t="inlineStr"/>
-      <c r="X17" s="5" t="inlineStr">
+      <c r="W17" s="4" t="inlineStr"/>
+      <c r="X17" s="4" t="inlineStr">
         <is>
           <t>CYBER</t>
         </is>
       </c>
-      <c r="Y17" s="5" t="inlineStr">
+      <c r="Y17" s="4" t="inlineStr">
         <is>
           <t>DATA_BREACH</t>
         </is>
       </c>
-      <c r="Z17" s="5" t="inlineStr">
+      <c r="Z17" s="4" t="inlineStr">
         <is>
           <t>data breach</t>
         </is>
       </c>
-      <c r="AA17" s="5" t="inlineStr">
+      <c r="AA17" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="5" t="inlineStr"/>
-      <c r="AC17" s="5" t="inlineStr">
+      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="AC17" s="4" t="inlineStr">
         <is>
           <t>04b77261a89eccd254c6e97b</t>
         </is>
       </c>
-      <c r="AD17" s="5" t="inlineStr">
+      <c r="AD17" s="4" t="inlineStr">
         <is>
           <t>95def5878b484fab12e3ab5e</t>
         </is>
       </c>
-      <c r="AE17" s="5" t="inlineStr"/>
-      <c r="AF17" s="5" t="inlineStr"/>
-      <c r="AG17" s="5" t="inlineStr"/>
-      <c r="AH17" s="5" t="inlineStr"/>
-      <c r="AI17" s="5" t="inlineStr"/>
-      <c r="AJ17" s="5" t="inlineStr"/>
-      <c r="AK17" s="5" t="inlineStr"/>
-      <c r="AL17" s="5" t="inlineStr"/>
-      <c r="AM17" s="5" t="inlineStr"/>
-      <c r="AN17" s="5" t="inlineStr"/>
-      <c r="AO17" s="5" t="inlineStr"/>
-      <c r="AP17" s="5" t="inlineStr"/>
-      <c r="AQ17" s="5" t="inlineStr"/>
-      <c r="AR17" s="5" t="inlineStr"/>
-      <c r="AS17" s="5" t="inlineStr"/>
-      <c r="AT17" s="5" t="inlineStr"/>
-      <c r="AU17" s="5" t="inlineStr"/>
-      <c r="AV17" s="5" t="inlineStr"/>
-      <c r="AW17" s="5" t="inlineStr"/>
-      <c r="AX17" s="5" t="inlineStr"/>
-      <c r="AY17" s="5" t="inlineStr"/>
-      <c r="AZ17" s="5" t="inlineStr"/>
-      <c r="BA17" s="5" t="inlineStr"/>
-      <c r="BB17" s="5" t="inlineStr">
+      <c r="AE17" s="4" t="inlineStr"/>
+      <c r="AF17" s="4" t="inlineStr"/>
+      <c r="AG17" s="4" t="inlineStr"/>
+      <c r="AH17" s="4" t="inlineStr"/>
+      <c r="AI17" s="4" t="inlineStr"/>
+      <c r="AJ17" s="4" t="inlineStr"/>
+      <c r="AK17" s="4" t="inlineStr"/>
+      <c r="AL17" s="4" t="inlineStr"/>
+      <c r="AM17" s="4" t="inlineStr"/>
+      <c r="AN17" s="4" t="inlineStr"/>
+      <c r="AO17" s="4" t="inlineStr"/>
+      <c r="AP17" s="4" t="inlineStr"/>
+      <c r="AQ17" s="4" t="inlineStr"/>
+      <c r="AR17" s="4" t="inlineStr"/>
+      <c r="AS17" s="4" t="inlineStr"/>
+      <c r="AT17" s="4" t="inlineStr"/>
+      <c r="AU17" s="4" t="inlineStr"/>
+      <c r="AV17" s="4" t="inlineStr"/>
+      <c r="AW17" s="4" t="inlineStr"/>
+      <c r="AX17" s="4" t="inlineStr"/>
+      <c r="AY17" s="4" t="inlineStr"/>
+      <c r="AZ17" s="4" t="inlineStr"/>
+      <c r="BA17" s="4" t="inlineStr"/>
+      <c r="BB17" s="4" t="inlineStr">
         <is>
           <t>APO</t>
         </is>
       </c>
-      <c r="BC17" s="5" t="inlineStr">
+      <c r="BC17" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD17" s="5" t="inlineStr"/>
-      <c r="BE17" s="5" t="inlineStr">
+      <c r="BD17" s="4" t="inlineStr"/>
+      <c r="BE17" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF17" s="5" t="inlineStr"/>
-      <c r="BG17" s="5" t="inlineStr">
+      <c r="BF17" s="4" t="inlineStr"/>
+      <c r="BG17" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH17" s="5" t="inlineStr"/>
+      <c r="BH17" s="4" t="inlineStr"/>
+      <c r="BI17" s="4" t="inlineStr"/>
+      <c r="BJ17" s="4" t="inlineStr"/>
+      <c r="BK17" s="4" t="inlineStr"/>
+      <c r="BL17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3695,6 +3895,10 @@
       <c r="BF18" s="2" t="inlineStr"/>
       <c r="BG18" s="2" t="inlineStr"/>
       <c r="BH18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BJ18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr"/>
+      <c r="BL18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -3849,516 +4053,572 @@
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
+      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr"/>
+      <c r="BL19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>TSN</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Tyson Foods, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>2026-08-21T01:31:00+08:00</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Tyson Foods WARN Act Investigation: Joslin Plant Layoffs and Legal Scrutiny - News and Statistics</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>裁員或人力縮減</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr"/>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>'-0.792</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr"/>
-      <c r="Q20" s="5" t="inlineStr"/>
-      <c r="R20" s="5" t="inlineStr"/>
-      <c r="S20" s="5" t="inlineStr"/>
-      <c r="T20" s="5" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr"/>
+      <c r="Q20" s="4" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="inlineStr"/>
+      <c r="T20" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U20" s="5" t="inlineStr">
+      <c r="U20" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNa01QZE1lcWZ3XzJjYkMtU1BuUDdBVi1KRkpGbWhpNzZIRmd4UjRFdWFucjRhdTkxcUc4WU91bDlwVjV3YkJGaUFSeUxnbTE5dVg4Tnh0LUU5TUFXNFIzLWdVM3ZoMEV6MUVvX29Lem9lVmNMUHJjNUdoZ3dlUFNsbGN5MGVtNU95WGtSdjF1cHdtZVNxRHgzT0NzbTk?oc=5</t>
         </is>
       </c>
-      <c r="V20" s="5" t="inlineStr">
+      <c r="V20" s="4" t="inlineStr">
         <is>
           <t>indexbox.io</t>
         </is>
       </c>
-      <c r="W20" s="5" t="inlineStr"/>
-      <c r="X20" s="5" t="inlineStr">
+      <c r="W20" s="4" t="inlineStr"/>
+      <c r="X20" s="4" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y20" s="5" t="inlineStr">
+      <c r="Y20" s="4" t="inlineStr">
         <is>
           <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
-      <c r="Z20" s="5" t="inlineStr">
+      <c r="Z20" s="4" t="inlineStr">
         <is>
           <t>layoff；layoffs</t>
         </is>
       </c>
-      <c r="AA20" s="5" t="inlineStr">
+      <c r="AA20" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB20" s="5" t="inlineStr"/>
-      <c r="AC20" s="5" t="inlineStr">
+      <c r="AB20" s="4" t="inlineStr"/>
+      <c r="AC20" s="4" t="inlineStr">
         <is>
           <t>cb7e61d4f6747c426ab2f6de</t>
         </is>
       </c>
-      <c r="AD20" s="5" t="inlineStr">
+      <c r="AD20" s="4" t="inlineStr">
         <is>
           <t>2b6bd383b14b865532023325</t>
         </is>
       </c>
-      <c r="AE20" s="5" t="inlineStr"/>
-      <c r="AF20" s="5" t="inlineStr"/>
-      <c r="AG20" s="5" t="inlineStr"/>
-      <c r="AH20" s="5" t="inlineStr"/>
-      <c r="AI20" s="5" t="inlineStr"/>
-      <c r="AJ20" s="5" t="inlineStr"/>
-      <c r="AK20" s="5" t="inlineStr"/>
-      <c r="AL20" s="5" t="inlineStr"/>
-      <c r="AM20" s="5" t="inlineStr"/>
-      <c r="AN20" s="5" t="inlineStr"/>
-      <c r="AO20" s="5" t="inlineStr"/>
-      <c r="AP20" s="5" t="inlineStr"/>
-      <c r="AQ20" s="5" t="inlineStr"/>
-      <c r="AR20" s="5" t="inlineStr"/>
-      <c r="AS20" s="5" t="inlineStr"/>
-      <c r="AT20" s="5" t="inlineStr"/>
-      <c r="AU20" s="5" t="inlineStr"/>
-      <c r="AV20" s="5" t="inlineStr"/>
-      <c r="AW20" s="5" t="inlineStr">
+      <c r="AE20" s="4" t="inlineStr"/>
+      <c r="AF20" s="4" t="inlineStr"/>
+      <c r="AG20" s="4" t="inlineStr"/>
+      <c r="AH20" s="4" t="inlineStr"/>
+      <c r="AI20" s="4" t="inlineStr"/>
+      <c r="AJ20" s="4" t="inlineStr"/>
+      <c r="AK20" s="4" t="inlineStr"/>
+      <c r="AL20" s="4" t="inlineStr"/>
+      <c r="AM20" s="4" t="inlineStr"/>
+      <c r="AN20" s="4" t="inlineStr"/>
+      <c r="AO20" s="4" t="inlineStr"/>
+      <c r="AP20" s="4" t="inlineStr"/>
+      <c r="AQ20" s="4" t="inlineStr"/>
+      <c r="AR20" s="4" t="inlineStr"/>
+      <c r="AS20" s="4" t="inlineStr"/>
+      <c r="AT20" s="4" t="inlineStr"/>
+      <c r="AU20" s="4" t="inlineStr"/>
+      <c r="AV20" s="4" t="inlineStr"/>
+      <c r="AW20" s="4" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX20" s="5" t="inlineStr"/>
-      <c r="AY20" s="5" t="inlineStr"/>
-      <c r="AZ20" s="5" t="inlineStr"/>
-      <c r="BA20" s="5" t="inlineStr"/>
-      <c r="BB20" s="5" t="inlineStr">
+      <c r="AX20" s="4" t="inlineStr"/>
+      <c r="AY20" s="4" t="inlineStr"/>
+      <c r="AZ20" s="4" t="inlineStr"/>
+      <c r="BA20" s="4" t="inlineStr"/>
+      <c r="BB20" s="4" t="inlineStr">
         <is>
           <t>TSN</t>
         </is>
       </c>
-      <c r="BC20" s="5" t="inlineStr">
+      <c r="BC20" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD20" s="5" t="inlineStr"/>
-      <c r="BE20" s="5" t="inlineStr">
+      <c r="BD20" s="4" t="inlineStr"/>
+      <c r="BE20" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF20" s="5" t="inlineStr">
+      <c r="BF20" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG20" s="5" t="inlineStr">
+      <c r="BG20" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH20" s="5" t="inlineStr"/>
+      <c r="BH20" s="4" t="inlineStr"/>
+      <c r="BI20" s="4" t="inlineStr"/>
+      <c r="BJ20" s="4" t="inlineStr"/>
+      <c r="BK20" s="4" t="inlineStr"/>
+      <c r="BL20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>PNR</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Pentair</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>2026-08-21T01:03:00+08:00</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>PNR Investor Alert: Pentair plc Securities Class Action Notice - Contact SueWallSt</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>'-0.082</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU2gyTWQ0ZnNBbHZ4N20waVVWNi1RZUsxMC1QNG9sT1FnelpqS0U1VkpHd1Y2bldEZlZ1YU1aSnBDUGFDZDc2ZS1SNUhYM1JhMkVNb3BHc1N3MFB5WFhIdTRYS0M1Y0hoeHVKLXg4d1RsZWVkSE90bkk2dTFXUnZHQzh5Q2N1Ym4zWjJIb2JzUlR1bG1VeHVudF9lbi1JaHRGdi12RnFIby1CeFB2WDVpVkhlZzdjZmRuUzJPSk5pc1JSS0dWSndmNXY0V2VjeTdELWxR?oc=5</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>prnewswire.com</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr"/>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>926ee65c0b0d4401ad96e40eb04c54e8</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>8aa08a7984611e910a09011d</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>784e9e349fa690e0b9d8c895</t>
+        </is>
+      </c>
+      <c r="AE21" s="3" t="inlineStr"/>
+      <c r="AF21" s="3" t="inlineStr"/>
+      <c r="AG21" s="3" t="inlineStr"/>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
+      <c r="AM21" s="3" t="inlineStr"/>
+      <c r="AN21" s="3" t="inlineStr"/>
+      <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>'-0.082</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU2gyTWQ0ZnNBbHZ4N20waVVWNi1RZUsxMC1QNG9sT1FnelpqS0U1VkpHd1Y2bldEZlZ1YU1aSnBDUGFDZDc2ZS1SNUhYM1JhMkVNb3BHc1N3MFB5WFhIdTRYS0M1Y0hoeHVKLXg4d1RsZWVkSE90bkk2dTFXUnZHQzh5Q2N1Ym4zWjJIb2JzUlR1bG1VeHVudF9lbi1JaHRGdi12RnFIby1CeFB2WDVpVkhlZzdjZmRuUzJPSk5pc1JSS0dWSndmNXY0V2VjeTdELWxR?oc=5</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="inlineStr">
-        <is>
-          <t>prnewswire.com</t>
-        </is>
-      </c>
-      <c r="W21" s="4" t="inlineStr"/>
-      <c r="X21" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y21" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z21" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA21" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="4" t="inlineStr"/>
-      <c r="AC21" s="4" t="inlineStr">
-        <is>
-          <t>8aa08a7984611e910a09011d</t>
-        </is>
-      </c>
-      <c r="AD21" s="4" t="inlineStr">
-        <is>
-          <t>784e9e349fa690e0b9d8c895</t>
-        </is>
-      </c>
-      <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="4" t="inlineStr"/>
-      <c r="AG21" s="4" t="inlineStr"/>
-      <c r="AH21" s="4" t="inlineStr"/>
-      <c r="AI21" s="4" t="inlineStr"/>
-      <c r="AJ21" s="4" t="inlineStr"/>
-      <c r="AK21" s="4" t="inlineStr"/>
-      <c r="AL21" s="4" t="inlineStr"/>
-      <c r="AM21" s="4" t="inlineStr"/>
-      <c r="AN21" s="4" t="inlineStr"/>
-      <c r="AO21" s="4" t="inlineStr"/>
-      <c r="AP21" s="4" t="inlineStr"/>
-      <c r="AQ21" s="4" t="inlineStr"/>
-      <c r="AR21" s="4" t="inlineStr"/>
-      <c r="AS21" s="4" t="inlineStr"/>
-      <c r="AT21" s="4" t="inlineStr"/>
-      <c r="AU21" s="4" t="inlineStr"/>
-      <c r="AV21" s="4" t="inlineStr"/>
-      <c r="AW21" s="4" t="inlineStr"/>
-      <c r="AX21" s="4" t="inlineStr"/>
-      <c r="AY21" s="4" t="inlineStr"/>
-      <c r="AZ21" s="4" t="inlineStr"/>
-      <c r="BA21" s="4" t="inlineStr"/>
-      <c r="BB21" s="4" t="inlineStr">
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr"/>
+      <c r="AS21" s="3" t="inlineStr"/>
+      <c r="AT21" s="3" t="inlineStr"/>
+      <c r="AU21" s="3" t="inlineStr"/>
+      <c r="AV21" s="3" t="inlineStr"/>
+      <c r="AW21" s="3" t="inlineStr"/>
+      <c r="AX21" s="3" t="inlineStr"/>
+      <c r="AY21" s="3" t="inlineStr"/>
+      <c r="AZ21" s="3" t="inlineStr"/>
+      <c r="BA21" s="3" t="inlineStr"/>
+      <c r="BB21" s="3" t="inlineStr">
         <is>
           <t>PNR</t>
         </is>
       </c>
-      <c r="BC21" s="4" t="inlineStr">
+      <c r="BC21" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD21" s="4" t="inlineStr"/>
-      <c r="BE21" s="4" t="inlineStr">
+      <c r="BD21" s="3" t="inlineStr"/>
+      <c r="BE21" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF21" s="4" t="inlineStr"/>
-      <c r="BG21" s="4" t="inlineStr">
+      <c r="BF21" s="3" t="inlineStr"/>
+      <c r="BG21" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH21" s="4" t="inlineStr"/>
+      <c r="BH21" s="3" t="inlineStr"/>
+      <c r="BI21" s="3" t="inlineStr"/>
+      <c r="BJ21" s="3" t="inlineStr"/>
+      <c r="BK21" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Walt Disney Company (The)</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>2026-08-21T00:36:53+08:00</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>美國司法部反對在迪士尼ABC執照訴訟案中立即舉行聽證會</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr"/>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/symbols/NYSE-DIS/news/</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr"/>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>3b037c4187df46bfa3bf8be5c20b95f5</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>ccb1ebcf32716240912f85bd</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr">
+        <is>
+          <t>c937b4988a142cad289af5a8</t>
+        </is>
+      </c>
+      <c r="AE22" s="3" t="inlineStr"/>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr"/>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr"/>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr"/>
+      <c r="AM22" s="3" t="inlineStr"/>
+      <c r="AN22" s="3" t="inlineStr"/>
+      <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr"/>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="4" t="inlineStr"/>
-      <c r="R22" s="4" t="inlineStr"/>
-      <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="4" t="inlineStr">
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr"/>
+      <c r="AS22" s="3" t="inlineStr"/>
+      <c r="AT22" s="3" t="inlineStr"/>
+      <c r="AU22" s="3" t="inlineStr"/>
+      <c r="AV22" s="3" t="inlineStr"/>
+      <c r="AW22" s="3" t="inlineStr"/>
+      <c r="AX22" s="3" t="inlineStr"/>
+      <c r="AY22" s="3" t="inlineStr"/>
+      <c r="AZ22" s="3" t="inlineStr"/>
+      <c r="BA22" s="3" t="inlineStr"/>
+      <c r="BB22" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="BC22" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-DIS/news/</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W22" s="4" t="inlineStr"/>
-      <c r="X22" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y22" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z22" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA22" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="4" t="inlineStr"/>
-      <c r="AC22" s="4" t="inlineStr">
-        <is>
-          <t>ccb1ebcf32716240912f85bd</t>
-        </is>
-      </c>
-      <c r="AD22" s="4" t="inlineStr">
-        <is>
-          <t>c937b4988a142cad289af5a8</t>
-        </is>
-      </c>
-      <c r="AE22" s="4" t="inlineStr"/>
-      <c r="AF22" s="4" t="inlineStr"/>
-      <c r="AG22" s="4" t="inlineStr"/>
-      <c r="AH22" s="4" t="inlineStr"/>
-      <c r="AI22" s="4" t="inlineStr"/>
-      <c r="AJ22" s="4" t="inlineStr"/>
-      <c r="AK22" s="4" t="inlineStr"/>
-      <c r="AL22" s="4" t="inlineStr"/>
-      <c r="AM22" s="4" t="inlineStr"/>
-      <c r="AN22" s="4" t="inlineStr"/>
-      <c r="AO22" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP22" s="4" t="inlineStr"/>
-      <c r="AQ22" s="4" t="inlineStr"/>
-      <c r="AR22" s="4" t="inlineStr"/>
-      <c r="AS22" s="4" t="inlineStr"/>
-      <c r="AT22" s="4" t="inlineStr"/>
-      <c r="AU22" s="4" t="inlineStr"/>
-      <c r="AV22" s="4" t="inlineStr"/>
-      <c r="AW22" s="4" t="inlineStr"/>
-      <c r="AX22" s="4" t="inlineStr"/>
-      <c r="AY22" s="4" t="inlineStr"/>
-      <c r="AZ22" s="4" t="inlineStr"/>
-      <c r="BA22" s="4" t="inlineStr"/>
-      <c r="BB22" s="4" t="inlineStr">
+      <c r="BD22" s="3" t="inlineStr">
         <is>
           <t>DIS</t>
         </is>
       </c>
-      <c r="BC22" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD22" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BE22" s="4" t="inlineStr">
+      <c r="BE22" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF22" s="4" t="inlineStr">
+      <c r="BF22" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG22" s="4" t="inlineStr"/>
-      <c r="BH22" s="4" t="inlineStr"/>
+      <c r="BG22" s="3" t="inlineStr"/>
+      <c r="BH22" s="3" t="inlineStr"/>
+      <c r="BI22" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ22" s="3" t="inlineStr"/>
+      <c r="BK22" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4533,175 +4793,203 @@
       </c>
       <c r="BG23" s="2" t="inlineStr"/>
       <c r="BH23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr"/>
+      <c r="BJ23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr"/>
+      <c r="BL23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>PNR</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Pentair</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>2026-08-21T00:00:00+08:00</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Pentair plc Investors to Act: Class Action Filed Alleging Investor Harm</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>'-0.724</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxQTGJNY0lvNl9HUGY1NWdDSWxZa3I4a04tMlJNcm02ZW1zVlR0MGY0bVZVdzYtUXBhQXlIVHZZcGI0SVVySW1pYjBpdnMxdkVHRC1sb21CdGxrVEN4M2RTVWJrcFpHdmxNNkJKWDhWVVZJanZOczhhcFNCSUhqQzd1MWlYZzBlOVg3TnduREZLSk5GVHIxajZxZjZtTTJfYzdBUHoxLWFpVjg3R2h3ZXZCVV9Qa3MtNXFVLVpaSlVYaTNXbHFaUUc2SUlFcmZtcUM2b05ZTmNxTVZCb3pZcUY5QlRxdXlTUzJhR3R6OEZzVnBZZDVua1hjTk10M0h0ODR1d3RVSTUxVG9XYkhYMGZJ?oc=5</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr"/>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>74f8ba1ec0284aeba251ba7b53cf0c51</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>37237c9b76e3a0aef2ac53db</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr">
+        <is>
+          <t>c5cc7637cf9a5876b35c475c</t>
+        </is>
+      </c>
+      <c r="AE24" s="3" t="inlineStr"/>
+      <c r="AF24" s="3" t="inlineStr"/>
+      <c r="AG24" s="3" t="inlineStr"/>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
+      <c r="AM24" s="3" t="inlineStr"/>
+      <c r="AN24" s="3" t="inlineStr"/>
+      <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>'-0.724</t>
-        </is>
-      </c>
-      <c r="P24" s="4" t="inlineStr"/>
-      <c r="Q24" s="4" t="inlineStr"/>
-      <c r="R24" s="4" t="inlineStr"/>
-      <c r="S24" s="4" t="inlineStr"/>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxQTGJNY0lvNl9HUGY1NWdDSWxZa3I4a04tMlJNcm02ZW1zVlR0MGY0bVZVdzYtUXBhQXlIVHZZcGI0SVVySW1pYjBpdnMxdkVHRC1sb21CdGxrVEN4M2RTVWJrcFpHdmxNNkJKWDhWVVZJanZOczhhcFNCSUhqQzd1MWlYZzBlOVg3TnduREZLSk5GVHIxajZxZjZtTTJfYzdBUHoxLWFpVjg3R2h3ZXZCVV9Qa3MtNXFVLVpaSlVYaTNXbHFaUUc2SUlFcmZtcUM2b05ZTmNxTVZCb3pZcUY5QlRxdXlTUzJhR3R6OEZzVnBZZDVua1hjTk10M0h0ODR1d3RVSTUxVG9XYkhYMGZJ?oc=5</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>GlobeNewswire</t>
-        </is>
-      </c>
-      <c r="W24" s="4" t="inlineStr"/>
-      <c r="X24" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y24" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z24" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA24" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="4" t="inlineStr"/>
-      <c r="AC24" s="4" t="inlineStr">
-        <is>
-          <t>37237c9b76e3a0aef2ac53db</t>
-        </is>
-      </c>
-      <c r="AD24" s="4" t="inlineStr">
-        <is>
-          <t>c5cc7637cf9a5876b35c475c</t>
-        </is>
-      </c>
-      <c r="AE24" s="4" t="inlineStr"/>
-      <c r="AF24" s="4" t="inlineStr"/>
-      <c r="AG24" s="4" t="inlineStr"/>
-      <c r="AH24" s="4" t="inlineStr"/>
-      <c r="AI24" s="4" t="inlineStr"/>
-      <c r="AJ24" s="4" t="inlineStr"/>
-      <c r="AK24" s="4" t="inlineStr"/>
-      <c r="AL24" s="4" t="inlineStr"/>
-      <c r="AM24" s="4" t="inlineStr"/>
-      <c r="AN24" s="4" t="inlineStr"/>
-      <c r="AO24" s="4" t="inlineStr"/>
-      <c r="AP24" s="4" t="inlineStr"/>
-      <c r="AQ24" s="4" t="inlineStr"/>
-      <c r="AR24" s="4" t="inlineStr"/>
-      <c r="AS24" s="4" t="inlineStr"/>
-      <c r="AT24" s="4" t="inlineStr"/>
-      <c r="AU24" s="4" t="inlineStr"/>
-      <c r="AV24" s="4" t="inlineStr"/>
-      <c r="AW24" s="4" t="inlineStr"/>
-      <c r="AX24" s="4" t="inlineStr"/>
-      <c r="AY24" s="4" t="inlineStr"/>
-      <c r="AZ24" s="4" t="inlineStr"/>
-      <c r="BA24" s="4" t="inlineStr"/>
-      <c r="BB24" s="4" t="inlineStr">
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr"/>
+      <c r="AS24" s="3" t="inlineStr"/>
+      <c r="AT24" s="3" t="inlineStr"/>
+      <c r="AU24" s="3" t="inlineStr"/>
+      <c r="AV24" s="3" t="inlineStr"/>
+      <c r="AW24" s="3" t="inlineStr"/>
+      <c r="AX24" s="3" t="inlineStr"/>
+      <c r="AY24" s="3" t="inlineStr"/>
+      <c r="AZ24" s="3" t="inlineStr"/>
+      <c r="BA24" s="3" t="inlineStr"/>
+      <c r="BB24" s="3" t="inlineStr">
         <is>
           <t>PNR</t>
         </is>
       </c>
-      <c r="BC24" s="4" t="inlineStr">
+      <c r="BC24" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD24" s="4" t="inlineStr"/>
-      <c r="BE24" s="4" t="inlineStr">
+      <c r="BD24" s="3" t="inlineStr"/>
+      <c r="BE24" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF24" s="4" t="inlineStr"/>
-      <c r="BG24" s="4" t="inlineStr">
+      <c r="BF24" s="3" t="inlineStr"/>
+      <c r="BG24" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH24" s="4" t="inlineStr"/>
+      <c r="BH24" s="3" t="inlineStr"/>
+      <c r="BI24" s="3" t="inlineStr"/>
+      <c r="BJ24" s="3" t="inlineStr"/>
+      <c r="BK24" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH24"/>
+  <autoFilter ref="A1:BL24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4712,7 +5000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BL11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4775,6 +5063,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5078,6 +5370,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -5092,12 +5404,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Automatic Data Processing, Inc.</t>
+          <t>Bank of America Corporation Common Stock</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -5107,18 +5419,18 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Fantasy Football ADP: Exploiting Default Rankings for 2026</t>
+          <t>SEC charges former Bank of America investment banker with insider trading</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>違約</t>
+          <t>內線交易</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -5128,13 +5440,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -5144,7 +5460,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>'-0.722</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
@@ -5158,40 +5474,44 @@
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNZ0VpOXBNeW51MDZ4ZjlwMFhZZU1xTVlxczBhVmI0UVc4VjRkQTZ6RktTSEtIbFNTeFBqQWJja0xFNVh2a1ljMk11dkVYV3R0S3VzVFhmV2tMUFBPLUJQeElFZThmOWlGZkNHRVBEb19IbnBQYUhmSUpLTkd2djBadV8tMzFkM1FyMlFjc1lkX00wckFsYlgtZ3NJRV9aby1DaHpwV2Q5RXlPaG81elE4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOMU4yOXN1ZWhTdkplbWUwX2xldjh1TWxjN3NCOUhJNjdzR1JKYzZZeGR4SHdjc1Q5elpCUFJQdXFwMmtyZ29jMTFnUXFxTExpSGZ6TUtZT3BCZEtaQXZkbFRhMTFrNGtqUlVobWZVSjltQXhfZHdERzlwNXlfS3F5WENBRUsxc3l0QmRFR0J5VmItVDdnOHpkVV9ESUEzMUpfRVlnOFA1b0NmeER3SWhPaXcyM3N5YzAzVDdoRzRKWkw?oc=5</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>RotoWire</t>
+          <t>Reuters</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr"/>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>FINANCIAL</t>
+          <t>GOVERNANCE</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>INSIDER_TRADING</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>default</t>
+          <t>insider trading</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>df0a320ae25f4a5da149a50349a707ca</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>b2c1a94eaab81f88a6c05a9c</t>
+          <t>3a4ca9a95155b8245d865ddc</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>6b8fda4a1b3b10248ded95ba</t>
+          <t>cb26369e7afea25be8d4a326</t>
         </is>
       </c>
       <c r="AE2" s="3" t="inlineStr"/>
@@ -5204,7 +5524,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -5214,7 +5538,7 @@
       <c r="AV2" s="3" t="inlineStr"/>
       <c r="AW2" s="3" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="AX2" s="3" t="inlineStr"/>
@@ -5223,7 +5547,7 @@
       <c r="BA2" s="3" t="inlineStr"/>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>BAC</t>
         </is>
       </c>
       <c r="BC2" s="3" t="inlineStr">
@@ -5234,12 +5558,12 @@
       <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
       <c r="BF2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
       <c r="BG2" s="3" t="inlineStr">
@@ -5248,176 +5572,212 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Bank of America Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>EFX</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Equifax, Inc. Common Stock</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>2026-08-21T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>SEC charges former Bank of America investment banker with insider trading</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Equifax agrees to $100M deal to end class action claims over credit score error</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>內線交易</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>0.83</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOV0tZQUdjZmhXS3k3YmU1UWFEY2NRWEJWQzRrekhxdFcwZTNicF84TzdiMTRVdnRZSEZyY0UxTzJMazhVRUdPTUhmRU0tR3ZpUjFqWk9vZmhjMXlSdFVkdmIxNGVaa3BqSWVDWGJFRTZaekFkZTk0M0QtUzRCUFhaMVBlWUFXZENSUFRIQkZZbVFtN3lVWFY1S1ktZlZMaF82LW1Oa0tWM0xpTGJUZzVValRpZjAyekZtVmRHVzVCdWRRQmJBZ1BPcFFKTEV3RldGdVI1ZXlmQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Top Class Actions</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>2e1eb4eaea9f470b874805250104f5d4</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>a93ac553e37f4eeb8a503b0e</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>ec8e6b1a1b1c66ac1d45db71</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>'-0.722</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOMU4yOXN1ZWhTdkplbWUwX2xldjh1TWxjN3NCOUhJNjdzR1JKYzZZeGR4SHdjc1Q5elpCUFJQdXFwMmtyZ29jMTFnUXFxTExpSGZ6TUtZT3BCZEtaQXZkbFRhMTFrNGtqUlVobWZVSjltQXhfZHdERzlwNXlfS3F5WENBRUsxc3l0QmRFR0J5VmItVDdnOHpkVV9ESUEzMUpfRVlnOFA1b0NmeER3SWhPaXcyM3N5YzAzVDdoRzRKWkw?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>Reuters</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>GOVERNANCE</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>INSIDER_TRADING</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>insider trading</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>3a4ca9a95155b8245d865ddc</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>cb26369e7afea25be8d4a326</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX3" s="4" t="inlineStr"/>
-      <c r="AY3" s="4" t="inlineStr"/>
-      <c r="AZ3" s="4" t="inlineStr"/>
-      <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr">
-        <is>
-          <t>BAC</t>
-        </is>
-      </c>
-      <c r="BC3" s="4" t="inlineStr">
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>EFX</t>
+        </is>
+      </c>
+      <c r="BC3" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="4" t="inlineStr"/>
-      <c r="BE3" s="4" t="inlineStr">
+      <c r="BD3" s="3" t="inlineStr"/>
+      <c r="BE3" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="4" t="inlineStr">
+      <c r="BF3" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="4" t="inlineStr">
+      <c r="BG3" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -5432,12 +5792,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Equifax, Inc. Common Stock</t>
+          <t>Clorox</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -5447,23 +5807,23 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Equifax agrees to $100M deal to end class action claims over credit score error</t>
+          <t>Is Clorox Stock Worth Buying as GOJO Growth Meets Margin Pressure?</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>營運惡化</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -5484,7 +5844,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.213</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr"/>
@@ -5498,40 +5858,40 @@
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOV0tZQUdjZmhXS3k3YmU1UWFEY2NRWEJWQzRrekhxdFcwZTNicF84TzdiMTRVdnRZSEZyY0UxTzJMazhVRUdPTUhmRU0tR3ZpUjFqWk9vZmhjMXlSdFVkdmIxNGVaa3BqSWVDWGJFRTZaekFkZTk0M0QtUzRCUFhaMVBlWUFXZENSUFRIQkZZbVFtN3lVWFY1S1ktZlZMaF82LW1Oa0tWM0xpTGJUZzVValRpZjAyekZtVmRHVzVCdWRRQmJBZ1BPcFFKTEV3RldGdVI1ZXlmQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORDA1M0V5STZJYnZjTzdCSVdPQkhvSS1qa0J5VThsVkFHbnNUaUdScFUtQmZLSkxJT0VSS2loLTZ1QVVaUjM4VkRqRjJicTk1b3BjeFBVZFE4QVE1bDZObTJZQm40Y2NyQW9XYXhNdnRRMXd1dUNJS05Yak5JdkVHS3BYdXVYNHFyMGtkM1doQ1dPclhQT1VZbTV6Zw?oc=5</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
         <is>
-          <t>Top Class Actions</t>
+          <t>Yahoo Finance</t>
         </is>
       </c>
       <c r="W4" s="4" t="inlineStr"/>
       <c r="X4" s="4" t="inlineStr">
         <is>
-          <t>LEGAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y4" s="4" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>OPERATING_DETERIORATION</t>
         </is>
       </c>
       <c r="Z4" s="4" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>margin pressure</t>
         </is>
       </c>
       <c r="AA4" s="4" t="inlineStr"/>
       <c r="AB4" s="4" t="inlineStr"/>
       <c r="AC4" s="4" t="inlineStr">
         <is>
-          <t>a93ac553e37f4eeb8a503b0e</t>
+          <t>67227f019967c42a43b36773</t>
         </is>
       </c>
       <c r="AD4" s="4" t="inlineStr">
         <is>
-          <t>ec8e6b1a1b1c66ac1d45db71</t>
+          <t>b3bfb07265a165d7e7332a07</t>
         </is>
       </c>
       <c r="AE4" s="4" t="inlineStr"/>
@@ -5552,18 +5912,14 @@
       <c r="AT4" s="4" t="inlineStr"/>
       <c r="AU4" s="4" t="inlineStr"/>
       <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
+      <c r="AW4" s="4" t="inlineStr"/>
       <c r="AX4" s="4" t="inlineStr"/>
       <c r="AY4" s="4" t="inlineStr"/>
       <c r="AZ4" s="4" t="inlineStr"/>
       <c r="BA4" s="4" t="inlineStr"/>
       <c r="BB4" s="4" t="inlineStr">
         <is>
-          <t>EFX</t>
+          <t>CLX</t>
         </is>
       </c>
       <c r="BC4" s="4" t="inlineStr">
@@ -5574,348 +5930,400 @@
       <c r="BD4" s="4" t="inlineStr"/>
       <c r="BE4" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF4" s="4" t="inlineStr"/>
       <c r="BG4" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BI4" s="4" t="inlineStr"/>
+      <c r="BJ4" s="4" t="inlineStr"/>
+      <c r="BK4" s="4" t="inlineStr"/>
+      <c r="BL4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Clorox</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Is Clorox Stock Worth Buying as GOJO Growth Meets Margin Pressure?</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr"/>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Walt Disney Company (The)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:55:17+08:00</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>美司法部反對就迪士尼ABC牌照訴訟案舉行緊急聽證會</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2624496</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>7a286744031f4dfb8060d957459d14f1</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>153c67f9d747a4285d681ba3</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>3659fbbaa3cea9a8a2d4b980</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>0.213</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="5" t="inlineStr"/>
-      <c r="S5" s="5" t="inlineStr"/>
-      <c r="T5" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORDA1M0V5STZJYnZjTzdCSVdPQkhvSS1qa0J5VThsVkFHbnNUaUdScFUtQmZLSkxJT0VSS2loLTZ1QVVaUjM4VkRqRjJicTk1b3BjeFBVZFE4QVE1bDZObTJZQm40Y2NyQW9XYXhNdnRRMXd1dUNJS05Yak5JdkVHS3BYdXVYNHFyMGtkM1doQ1dPclhQT1VZbTV6Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W5" s="5" t="inlineStr"/>
-      <c r="X5" s="5" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="5" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="5" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA5" s="5" t="inlineStr"/>
-      <c r="AB5" s="5" t="inlineStr"/>
-      <c r="AC5" s="5" t="inlineStr">
-        <is>
-          <t>67227f019967c42a43b36773</t>
-        </is>
-      </c>
-      <c r="AD5" s="5" t="inlineStr">
-        <is>
-          <t>b3bfb07265a165d7e7332a07</t>
-        </is>
-      </c>
-      <c r="AE5" s="5" t="inlineStr"/>
-      <c r="AF5" s="5" t="inlineStr"/>
-      <c r="AG5" s="5" t="inlineStr"/>
-      <c r="AH5" s="5" t="inlineStr"/>
-      <c r="AI5" s="5" t="inlineStr"/>
-      <c r="AJ5" s="5" t="inlineStr"/>
-      <c r="AK5" s="5" t="inlineStr"/>
-      <c r="AL5" s="5" t="inlineStr"/>
-      <c r="AM5" s="5" t="inlineStr"/>
-      <c r="AN5" s="5" t="inlineStr"/>
-      <c r="AO5" s="5" t="inlineStr"/>
-      <c r="AP5" s="5" t="inlineStr"/>
-      <c r="AQ5" s="5" t="inlineStr"/>
-      <c r="AR5" s="5" t="inlineStr"/>
-      <c r="AS5" s="5" t="inlineStr"/>
-      <c r="AT5" s="5" t="inlineStr"/>
-      <c r="AU5" s="5" t="inlineStr"/>
-      <c r="AV5" s="5" t="inlineStr"/>
-      <c r="AW5" s="5" t="inlineStr"/>
-      <c r="AX5" s="5" t="inlineStr"/>
-      <c r="AY5" s="5" t="inlineStr"/>
-      <c r="AZ5" s="5" t="inlineStr"/>
-      <c r="BA5" s="5" t="inlineStr"/>
-      <c r="BB5" s="5" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="BC5" s="5" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD5" s="5" t="inlineStr"/>
-      <c r="BE5" s="5" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF5" s="5" t="inlineStr"/>
-      <c r="BG5" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH5" s="5" t="inlineStr"/>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr"/>
+      <c r="AX5" s="3" t="inlineStr"/>
+      <c r="AY5" s="3" t="inlineStr"/>
+      <c r="AZ5" s="3" t="inlineStr"/>
+      <c r="BA5" s="3" t="inlineStr"/>
+      <c r="BB5" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="BC5" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD5" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="BE5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG5" s="3" t="inlineStr"/>
+      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Walt Disney Company (The)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21T10:55:17+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>美司法部反對就迪士尼ABC牌照訴訟案舉行緊急聽證會</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Abbott Laboratories</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21T09:51:53+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>雅培將支付6.7億美元以了結部分早產兒配方奶粉訴訟</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2624374</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>9e313718274e4982b87c9e28823cbfe4</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>dbea804fa21928a28a097664</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>2c47dcd5fe84634ff135980b</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr"/>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr"/>
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2624496</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>153c67f9d747a4285d681ba3</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>3659fbbaa3cea9a8a2d4b980</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr"/>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BC6" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD6" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BE6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="4" t="inlineStr"/>
-      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BD6" s="3" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="BE6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
+        </is>
+      </c>
+      <c r="BF6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG6" s="3" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -5928,36 +6336,40 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>APO</t>
+        </is>
+      </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Apollo Global Management</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T09:51:53+08:00</t>
+          <t>2026-08-21T04:19:45+08:00</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>雅培將支付6.7億美元以了結部分早產兒配方奶粉訴訟</t>
+          <t>Apollo Global Management Data Breach Impacts SSNs; Lawsuit Possible</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>重大訴訟</t>
+          <t>資料外洩</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -5965,11 +6377,7 @@
           <t>規則</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
+      <c r="L7" s="4" t="inlineStr"/>
       <c r="M7" s="4" t="inlineStr">
         <is>
           <t>False</t>
@@ -5980,52 +6388,60 @@
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>'-0.933</t>
+        </is>
+      </c>
       <c r="P7" s="4" t="inlineStr"/>
       <c r="Q7" s="4" t="inlineStr"/>
       <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="4" t="inlineStr"/>
       <c r="T7" s="4" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>https://www.gelonghui.com/live/2624374</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNSGlaMkhFZWFObEtxVWo4MFdxSTBkZFJJWFU3Z3BKamRKa0VqRVBmWV9LY29pSy1YV29icjJwLWppRnVXZEMtMUFabGpRX2NYMGNBeHpvdDBDdFZZa2ZxY1dyaGFqcklCeUx2T09TcUFXWVVEUUltdGhBeDNlSzUteEtBMjFndVgxRllaZkhR?oc=5</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>classaction.org</t>
         </is>
       </c>
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>LEGAL</t>
+          <t>CYBER</t>
         </is>
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>MAJOR_LITIGATION</t>
+          <t>DATA_BREACH</t>
         </is>
       </c>
       <c r="Z7" s="4" t="inlineStr">
         <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="inlineStr"/>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB7" s="4" t="inlineStr"/>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>dbea804fa21928a28a097664</t>
+          <t>04b77261a89eccd254c6e97b</t>
         </is>
       </c>
       <c r="AD7" s="4" t="inlineStr">
         <is>
-          <t>2c47dcd5fe84634ff135980b</t>
+          <t>95def5878b484fab12e3ab5e</t>
         </is>
       </c>
       <c r="AE7" s="4" t="inlineStr"/>
@@ -6038,11 +6454,7 @@
       <c r="AL7" s="4" t="inlineStr"/>
       <c r="AM7" s="4" t="inlineStr"/>
       <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="AO7" s="4" t="inlineStr"/>
       <c r="AP7" s="4" t="inlineStr"/>
       <c r="AQ7" s="4" t="inlineStr"/>
       <c r="AR7" s="4" t="inlineStr"/>
@@ -6057,31 +6469,31 @@
       <c r="BA7" s="4" t="inlineStr"/>
       <c r="BB7" s="4" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>APO</t>
         </is>
       </c>
       <c r="BC7" s="4" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD7" s="4" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD7" s="4" t="inlineStr"/>
       <c r="BE7" s="4" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG7" s="4" t="inlineStr"/>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr"/>
+      <c r="BG7" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
       <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr"/>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr"/>
+      <c r="BL7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -6094,36 +6506,40 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>TSN</t>
+        </is>
+      </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>Tyson Foods, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T06:02:16+08:00</t>
+          <t>2026-08-21T01:31:00+08:00</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Federal prosecutors take over charges in Rutland murder case, won’t seek death penalty</t>
+          <t>Tyson Foods WARN Act Investigation: Joslin Plant Layoffs and Legal Scrutiny - News and Statistics</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -6131,11 +6547,7 @@
           <t>規則</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
+      <c r="L8" s="4" t="inlineStr"/>
       <c r="M8" s="4" t="inlineStr">
         <is>
           <t>False</t>
@@ -6148,7 +6560,7 @@
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>'-0.792</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr"/>
@@ -6157,33 +6569,33 @@
       <c r="S8" s="4" t="inlineStr"/>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQQWU4R0RnaXNHby02QmxXZDVmc0pWdkRZazREQzluNU1PV3YwRVlCX3dGaDJTYWxWY3J2ejl5SzNiaUlHS3B4cFFaSWloWVl0SGJyVjFpRFUtdjNQNGM0S2lQaWl5NW5BUzczNFdxNjRDUWFCRm4zaXZwbnVTaVRiS3YydWpnUVhHemFBbk13RjBhbG1mWTdzbE5DWDNkOThCd3QzUU85R0Exem43RlJFa05VbVYyM04t?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNa01QZE1lcWZ3XzJjYkMtU1BuUDdBVi1KRkpGbWhpNzZIRmd4UjRFdWFucjRhdTkxcUc4WU91bDlwVjV3YkJGaUFSeUxnbTE5dVg4Tnh0LUU5TUFXNFIzLWdVM3ZoMEV6MUVvX29Lem9lVmNMUHJjNUdoZ3dlUFNsbGN5MGVtNU95WGtSdjF1cHdtZVNxRHgzT0NzbTk?oc=5</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>vtdigger.org</t>
+          <t>indexbox.io</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>LEGAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z8" s="4" t="inlineStr">
         <is>
-          <t>penalty</t>
+          <t>layoff；layoffs</t>
         </is>
       </c>
       <c r="AA8" s="4" t="inlineStr">
@@ -6194,12 +6606,12 @@
       <c r="AB8" s="4" t="inlineStr"/>
       <c r="AC8" s="4" t="inlineStr">
         <is>
-          <t>05ae3052aa091667cf1b0b3c</t>
+          <t>cb7e61d4f6747c426ab2f6de</t>
         </is>
       </c>
       <c r="AD8" s="4" t="inlineStr">
         <is>
-          <t>d73878c04251aaaf0ee40892</t>
+          <t>2b6bd383b14b865532023325</t>
         </is>
       </c>
       <c r="AE8" s="4" t="inlineStr"/>
@@ -6212,11 +6624,7 @@
       <c r="AL8" s="4" t="inlineStr"/>
       <c r="AM8" s="4" t="inlineStr"/>
       <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="AO8" s="4" t="inlineStr"/>
       <c r="AP8" s="4" t="inlineStr"/>
       <c r="AQ8" s="4" t="inlineStr"/>
       <c r="AR8" s="4" t="inlineStr"/>
@@ -6224,26 +6632,26 @@
       <c r="AT8" s="4" t="inlineStr"/>
       <c r="AU8" s="4" t="inlineStr"/>
       <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX8" s="4" t="inlineStr"/>
       <c r="AY8" s="4" t="inlineStr"/>
       <c r="AZ8" s="4" t="inlineStr"/>
       <c r="BA8" s="4" t="inlineStr"/>
       <c r="BB8" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="BC8" s="4" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD8" s="4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD8" s="4" t="inlineStr"/>
       <c r="BE8" s="4" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
@@ -6254,853 +6662,593 @@
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG8" s="4" t="inlineStr"/>
+      <c r="BG8" s="4" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
       <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr"/>
+      <c r="BL8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>APO</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Apollo Global Management</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21T04:19:45+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Apollo Global Management Data Breach Impacts SSNs; Lawsuit Possible</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr"/>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:03:00+08:00</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>PNR Investor Alert: Pentair plc Securities Class Action Notice - Contact SueWallSt</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>'-0.082</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU2gyTWQ0ZnNBbHZ4N20waVVWNi1RZUsxMC1QNG9sT1FnelpqS0U1VkpHd1Y2bldEZlZ1YU1aSnBDUGFDZDc2ZS1SNUhYM1JhMkVNb3BHc1N3MFB5WFhIdTRYS0M1Y0hoeHVKLXg4d1RsZWVkSE90bkk2dTFXUnZHQzh5Q2N1Ym4zWjJIb2JzUlR1bG1VeHVudF9lbi1JaHRGdi12RnFIby1CeFB2WDVpVkhlZzdjZmRuUzJPSk5pc1JSS0dWSndmNXY0V2VjeTdELWxR?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>prnewswire.com</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>926ee65c0b0d4401ad96e40eb04c54e8</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>8aa08a7984611e910a09011d</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr">
+        <is>
+          <t>784e9e349fa690e0b9d8c895</t>
+        </is>
+      </c>
+      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AF9" s="3" t="inlineStr"/>
+      <c r="AG9" s="3" t="inlineStr"/>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr"/>
+      <c r="AM9" s="3" t="inlineStr"/>
+      <c r="AN9" s="3" t="inlineStr"/>
+      <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>'-0.933</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNSGlaMkhFZWFObEtxVWo4MFdxSTBkZFJJWFU3Z3BKamRKa0VqRVBmWV9LY29pSy1YV29icjJwLWppRnVXZEMtMUFabGpRX2NYMGNBeHpvdDBDdFZZa2ZxY1dyaGFqcklCeUx2T09TcUFXWVVEUUltdGhBeDNlSzUteEtBMjFndVgxRllaZkhR?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="5" t="inlineStr">
-        <is>
-          <t>classaction.org</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="inlineStr"/>
-      <c r="X9" s="5" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y9" s="5" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z9" s="5" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA9" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="5" t="inlineStr"/>
-      <c r="AC9" s="5" t="inlineStr">
-        <is>
-          <t>04b77261a89eccd254c6e97b</t>
-        </is>
-      </c>
-      <c r="AD9" s="5" t="inlineStr">
-        <is>
-          <t>95def5878b484fab12e3ab5e</t>
-        </is>
-      </c>
-      <c r="AE9" s="5" t="inlineStr"/>
-      <c r="AF9" s="5" t="inlineStr"/>
-      <c r="AG9" s="5" t="inlineStr"/>
-      <c r="AH9" s="5" t="inlineStr"/>
-      <c r="AI9" s="5" t="inlineStr"/>
-      <c r="AJ9" s="5" t="inlineStr"/>
-      <c r="AK9" s="5" t="inlineStr"/>
-      <c r="AL9" s="5" t="inlineStr"/>
-      <c r="AM9" s="5" t="inlineStr"/>
-      <c r="AN9" s="5" t="inlineStr"/>
-      <c r="AO9" s="5" t="inlineStr"/>
-      <c r="AP9" s="5" t="inlineStr"/>
-      <c r="AQ9" s="5" t="inlineStr"/>
-      <c r="AR9" s="5" t="inlineStr"/>
-      <c r="AS9" s="5" t="inlineStr"/>
-      <c r="AT9" s="5" t="inlineStr"/>
-      <c r="AU9" s="5" t="inlineStr"/>
-      <c r="AV9" s="5" t="inlineStr"/>
-      <c r="AW9" s="5" t="inlineStr"/>
-      <c r="AX9" s="5" t="inlineStr"/>
-      <c r="AY9" s="5" t="inlineStr"/>
-      <c r="AZ9" s="5" t="inlineStr"/>
-      <c r="BA9" s="5" t="inlineStr"/>
-      <c r="BB9" s="5" t="inlineStr">
-        <is>
-          <t>APO</t>
-        </is>
-      </c>
-      <c r="BC9" s="5" t="inlineStr">
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr"/>
+      <c r="AS9" s="3" t="inlineStr"/>
+      <c r="AT9" s="3" t="inlineStr"/>
+      <c r="AU9" s="3" t="inlineStr"/>
+      <c r="AV9" s="3" t="inlineStr"/>
+      <c r="AW9" s="3" t="inlineStr"/>
+      <c r="AX9" s="3" t="inlineStr"/>
+      <c r="AY9" s="3" t="inlineStr"/>
+      <c r="AZ9" s="3" t="inlineStr"/>
+      <c r="BA9" s="3" t="inlineStr"/>
+      <c r="BB9" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC9" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="5" t="inlineStr"/>
-      <c r="BE9" s="5" t="inlineStr">
+      <c r="BD9" s="3" t="inlineStr"/>
+      <c r="BE9" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF9" s="5" t="inlineStr"/>
-      <c r="BG9" s="5" t="inlineStr">
+      <c r="BF9" s="3" t="inlineStr"/>
+      <c r="BG9" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH9" s="5" t="inlineStr"/>
+      <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>TSN</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>Tyson Foods, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-21T01:31:00+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Tyson Foods WARN Act Investigation: Joslin Plant Layoffs and Legal Scrutiny - News and Statistics</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr"/>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Walt Disney Company (The)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21T00:36:53+08:00</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>美國司法部反對在迪士尼ABC執照訴訟案中立即舉行聽證會</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/symbols/NYSE-DIS/news/</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>3b037c4187df46bfa3bf8be5c20b95f5</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>ccb1ebcf32716240912f85bd</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>c937b4988a142cad289af5a8</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>'-0.792</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="inlineStr"/>
-      <c r="R10" s="5" t="inlineStr"/>
-      <c r="S10" s="5" t="inlineStr"/>
-      <c r="T10" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNa01QZE1lcWZ3XzJjYkMtU1BuUDdBVi1KRkpGbWhpNzZIRmd4UjRFdWFucjRhdTkxcUc4WU91bDlwVjV3YkJGaUFSeUxnbTE5dVg4Tnh0LUU5TUFXNFIzLWdVM3ZoMEV6MUVvX29Lem9lVmNMUHJjNUdoZ3dlUFNsbGN5MGVtNU95WGtSdjF1cHdtZVNxRHgzT0NzbTk?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="5" t="inlineStr">
-        <is>
-          <t>indexbox.io</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="inlineStr"/>
-      <c r="X10" s="5" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="5" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z10" s="5" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA10" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="5" t="inlineStr"/>
-      <c r="AC10" s="5" t="inlineStr">
-        <is>
-          <t>cb7e61d4f6747c426ab2f6de</t>
-        </is>
-      </c>
-      <c r="AD10" s="5" t="inlineStr">
-        <is>
-          <t>2b6bd383b14b865532023325</t>
-        </is>
-      </c>
-      <c r="AE10" s="5" t="inlineStr"/>
-      <c r="AF10" s="5" t="inlineStr"/>
-      <c r="AG10" s="5" t="inlineStr"/>
-      <c r="AH10" s="5" t="inlineStr"/>
-      <c r="AI10" s="5" t="inlineStr"/>
-      <c r="AJ10" s="5" t="inlineStr"/>
-      <c r="AK10" s="5" t="inlineStr"/>
-      <c r="AL10" s="5" t="inlineStr"/>
-      <c r="AM10" s="5" t="inlineStr"/>
-      <c r="AN10" s="5" t="inlineStr"/>
-      <c r="AO10" s="5" t="inlineStr"/>
-      <c r="AP10" s="5" t="inlineStr"/>
-      <c r="AQ10" s="5" t="inlineStr"/>
-      <c r="AR10" s="5" t="inlineStr"/>
-      <c r="AS10" s="5" t="inlineStr"/>
-      <c r="AT10" s="5" t="inlineStr"/>
-      <c r="AU10" s="5" t="inlineStr"/>
-      <c r="AV10" s="5" t="inlineStr"/>
-      <c r="AW10" s="5" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX10" s="5" t="inlineStr"/>
-      <c r="AY10" s="5" t="inlineStr"/>
-      <c r="AZ10" s="5" t="inlineStr"/>
-      <c r="BA10" s="5" t="inlineStr"/>
-      <c r="BB10" s="5" t="inlineStr">
-        <is>
-          <t>TSN</t>
-        </is>
-      </c>
-      <c r="BC10" s="5" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD10" s="5" t="inlineStr"/>
-      <c r="BE10" s="5" t="inlineStr">
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr"/>
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="BC10" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD10" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="BE10" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="5" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="5" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH10" s="5" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>PNR</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Pentair</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21T01:03:00+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>PNR Investor Alert: Pentair plc Securities Class Action Notice - Contact SueWallSt</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21T00:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Pentair plc Investors to Act: Class Action Filed Alleging Investor Harm</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>'-0.724</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxQTGJNY0lvNl9HUGY1NWdDSWxZa3I4a04tMlJNcm02ZW1zVlR0MGY0bVZVdzYtUXBhQXlIVHZZcGI0SVVySW1pYjBpdnMxdkVHRC1sb21CdGxrVEN4M2RTVWJrcFpHdmxNNkJKWDhWVVZJanZOczhhcFNCSUhqQzd1MWlYZzBlOVg3TnduREZLSk5GVHIxajZxZjZtTTJfYzdBUHoxLWFpVjg3R2h3ZXZCVV9Qa3MtNXFVLVpaSlVYaTNXbHFaUUc2SUlFcmZtcUM2b05ZTmNxTVZCb3pZcUY5QlRxdXlTUzJhR3R6OEZzVnBZZDVua1hjTk10M0h0ODR1d3RVSTUxVG9XYkhYMGZJ?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>GlobeNewswire</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>74f8ba1ec0284aeba251ba7b53cf0c51</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>37237c9b76e3a0aef2ac53db</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>c5cc7637cf9a5876b35c475c</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>'-0.082</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU2gyTWQ0ZnNBbHZ4N20waVVWNi1RZUsxMC1QNG9sT1FnelpqS0U1VkpHd1Y2bldEZlZ1YU1aSnBDUGFDZDc2ZS1SNUhYM1JhMkVNb3BHc1N3MFB5WFhIdTRYS0M1Y0hoeHVKLXg4d1RsZWVkSE90bkk2dTFXUnZHQzh5Q2N1Ym4zWjJIb2JzUlR1bG1VeHVudF9lbi1JaHRGdi12RnFIby1CeFB2WDVpVkhlZzdjZmRuUzJPSk5pc1JSS0dWSndmNXY0V2VjeTdELWxR?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>prnewswire.com</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>8aa08a7984611e910a09011d</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>784e9e349fa690e0b9d8c895</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr"/>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr">
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr"/>
+      <c r="AS11" s="3" t="inlineStr"/>
+      <c r="AT11" s="3" t="inlineStr"/>
+      <c r="AU11" s="3" t="inlineStr"/>
+      <c r="AV11" s="3" t="inlineStr"/>
+      <c r="AW11" s="3" t="inlineStr"/>
+      <c r="AX11" s="3" t="inlineStr"/>
+      <c r="AY11" s="3" t="inlineStr"/>
+      <c r="AZ11" s="3" t="inlineStr"/>
+      <c r="BA11" s="3" t="inlineStr"/>
+      <c r="BB11" s="3" t="inlineStr">
         <is>
           <t>PNR</t>
         </is>
       </c>
-      <c r="BC11" s="4" t="inlineStr">
+      <c r="BC11" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr">
+      <c r="BD11" s="3" t="inlineStr"/>
+      <c r="BE11" s="3" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF11" s="4" t="inlineStr"/>
-      <c r="BG11" s="4" t="inlineStr">
+      <c r="BF11" s="3" t="inlineStr"/>
+      <c r="BG11" s="3" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Walt Disney Company (The)</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21T00:36:53+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>美國司法部反對在迪士尼ABC執照訴訟案中立即舉行聽證會</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr"/>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-DIS/news/</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>ccb1ebcf32716240912f85bd</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>c937b4988a142cad289af5a8</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr"/>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BC12" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD12" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BE12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG12" s="4" t="inlineStr"/>
-      <c r="BH12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21T00:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Pentair plc Investors to Act: Class Action Filed Alleging Investor Harm</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr"/>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>'-0.724</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxQTGJNY0lvNl9HUGY1NWdDSWxZa3I4a04tMlJNcm02ZW1zVlR0MGY0bVZVdzYtUXBhQXlIVHZZcGI0SVVySW1pYjBpdnMxdkVHRC1sb21CdGxrVEN4M2RTVWJrcFpHdmxNNkJKWDhWVVZJanZOczhhcFNCSUhqQzd1MWlYZzBlOVg3TnduREZLSk5GVHIxajZxZjZtTTJfYzdBUHoxLWFpVjg3R2h3ZXZCVV9Qa3MtNXFVLVpaSlVYaTNXbHFaUUc2SUlFcmZtcUM2b05ZTmNxTVZCb3pZcUY5QlRxdXlTUzJhR3R6OEZzVnBZZDVua1hjTk10M0h0ODR1d3RVSTUxVG9XYkhYMGZJ?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>GlobeNewswire</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="4" t="inlineStr"/>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t>37237c9b76e3a0aef2ac53db</t>
-        </is>
-      </c>
-      <c r="AD13" s="4" t="inlineStr">
-        <is>
-          <t>c5cc7637cf9a5876b35c475c</t>
-        </is>
-      </c>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
-      <c r="AP13" s="4" t="inlineStr"/>
-      <c r="AQ13" s="4" t="inlineStr"/>
-      <c r="AR13" s="4" t="inlineStr"/>
-      <c r="AS13" s="4" t="inlineStr"/>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr"/>
-      <c r="AX13" s="4" t="inlineStr"/>
-      <c r="AY13" s="4" t="inlineStr"/>
-      <c r="AZ13" s="4" t="inlineStr"/>
-      <c r="BA13" s="4" t="inlineStr"/>
-      <c r="BB13" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC13" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD13" s="4" t="inlineStr"/>
-      <c r="BE13" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF13" s="4" t="inlineStr"/>
-      <c r="BG13" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH13" s="4" t="inlineStr"/>
+      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH13"/>
+  <autoFilter ref="A1:BL11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7111,7 +7259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7174,6 +7322,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7477,859 +7629,207 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Walt Disney Company (The)</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21T10:55:17+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>美司法部反對就迪士尼ABC牌照訴訟案舉行緊急聽證會</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Robinhood Markets</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21T00:02:39+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Mount Hood loses Level 1 evacuation as wildfire moves away</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>天災</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>僅紀錄</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr"/>
-      <c r="P2" s="4" t="inlineStr"/>
-      <c r="Q2" s="4" t="inlineStr"/>
-      <c r="R2" s="4" t="inlineStr"/>
-      <c r="S2" s="4" t="inlineStr"/>
-      <c r="T2" s="4" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>'-0.866</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2624496</t>
-        </is>
-      </c>
-      <c r="V2" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z2" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA2" s="4" t="inlineStr"/>
-      <c r="AB2" s="4" t="inlineStr"/>
-      <c r="AC2" s="4" t="inlineStr">
-        <is>
-          <t>153c67f9d747a4285d681ba3</t>
-        </is>
-      </c>
-      <c r="AD2" s="4" t="inlineStr">
-        <is>
-          <t>3659fbbaa3cea9a8a2d4b980</t>
-        </is>
-      </c>
-      <c r="AE2" s="4" t="inlineStr"/>
-      <c r="AF2" s="4" t="inlineStr"/>
-      <c r="AG2" s="4" t="inlineStr"/>
-      <c r="AH2" s="4" t="inlineStr"/>
-      <c r="AI2" s="4" t="inlineStr"/>
-      <c r="AJ2" s="4" t="inlineStr"/>
-      <c r="AK2" s="4" t="inlineStr"/>
-      <c r="AL2" s="4" t="inlineStr"/>
-      <c r="AM2" s="4" t="inlineStr"/>
-      <c r="AN2" s="4" t="inlineStr"/>
-      <c r="AO2" s="4" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPb1RvVkZ5MGZJQXVfaE5iSlJwX0hCT09zVlc0YkliWFNxYmFLM2tOUHN1ZThiTDJ3WnVpa254S2hvcWl2LTI5STRmREVxalliZWQ4d1p0Njk4bmZXQks4ZWM4ZFNmdXNuUk44bWVhYXZUTl9OdjVHQUZreUY0ZmZaenl1RlUxeF9kaXdEbkZjQnhYWkRvQkc5M2pWVEtvQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>youroregonnews.com</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>NATURAL_DISASTER</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>wildfire</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>f50677898d33941fa427d743</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>987a69de482d8d13094bacef</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AG2" s="2" t="inlineStr"/>
+      <c r="AH2" s="2" t="inlineStr"/>
+      <c r="AI2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AK2" s="2" t="inlineStr"/>
+      <c r="AL2" s="2" t="inlineStr"/>
+      <c r="AM2" s="2" t="inlineStr"/>
+      <c r="AN2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP2" s="4" t="inlineStr"/>
-      <c r="AQ2" s="4" t="inlineStr"/>
-      <c r="AR2" s="4" t="inlineStr"/>
-      <c r="AS2" s="4" t="inlineStr"/>
-      <c r="AT2" s="4" t="inlineStr"/>
-      <c r="AU2" s="4" t="inlineStr"/>
-      <c r="AV2" s="4" t="inlineStr"/>
-      <c r="AW2" s="4" t="inlineStr"/>
-      <c r="AX2" s="4" t="inlineStr"/>
-      <c r="AY2" s="4" t="inlineStr"/>
-      <c r="AZ2" s="4" t="inlineStr"/>
-      <c r="BA2" s="4" t="inlineStr"/>
-      <c r="BB2" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BC2" s="4" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr"/>
+      <c r="AQ2" s="2" t="inlineStr"/>
+      <c r="AR2" s="2" t="inlineStr"/>
+      <c r="AS2" s="2" t="inlineStr"/>
+      <c r="AT2" s="2" t="inlineStr"/>
+      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" s="2" t="inlineStr"/>
+      <c r="AX2" s="2" t="inlineStr"/>
+      <c r="AY2" s="2" t="inlineStr"/>
+      <c r="AZ2" s="2" t="inlineStr"/>
+      <c r="BA2" s="2" t="inlineStr"/>
+      <c r="BB2" s="2" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="BC2" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD2" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BE2" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="4" t="inlineStr"/>
-      <c r="BH2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Abbott Laboratories</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21T09:51:53+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>雅培將支付6.7億美元以了結部分早產兒配方奶粉訴訟</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2624374</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>dbea804fa21928a28a097664</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>2c47dcd5fe84634ff135980b</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr"/>
-      <c r="AX3" s="4" t="inlineStr"/>
-      <c r="AY3" s="4" t="inlineStr"/>
-      <c r="AZ3" s="4" t="inlineStr"/>
-      <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="BC3" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="4" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="BE3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
-        </is>
-      </c>
-      <c r="BF3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG3" s="4" t="inlineStr"/>
-      <c r="BH3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr"/>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21T06:02:16+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Federal prosecutors take over charges in Rutland murder case, won’t seek death penalty</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>0.005</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxQQWU4R0RnaXNHby02QmxXZDVmc0pWdkRZazREQzluNU1PV3YwRVlCX3dGaDJTYWxWY3J2ejl5SzNiaUlHS3B4cFFaSWloWVl0SGJyVjFpRFUtdjNQNGM0S2lQaWl5NW5BUzczNFdxNjRDUWFCRm4zaXZwbnVTaVRiS3YydWpnUVhHemFBbk13RjBhbG1mWTdzbE5DWDNkOThCd3QzUU85R0Exem43RlJFa05VbVYyM04t?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>vtdigger.org</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>penalty</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>05ae3052aa091667cf1b0b3c</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>d73878c04251aaaf0ee40892</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD4" s="4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="4" t="inlineStr"/>
-      <c r="BH4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Walt Disney Company (The)</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21T00:36:53+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>美國司法部反對在迪士尼ABC執照訴訟案中立即舉行聽證會</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-DIS/news/</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>ccb1ebcf32716240912f85bd</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>c937b4988a142cad289af5a8</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr"/>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BC5" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="4" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
-      <c r="BE5" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="4" t="inlineStr"/>
-      <c r="BH5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Robinhood Markets</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21T00:02:39+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Mount Hood loses Level 1 evacuation as wildfire moves away</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>'-0.866</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPb1RvVkZ5MGZJQXVfaE5iSlJwX0hCT09zVlc0YkliWFNxYmFLM2tOUHN1ZThiTDJ3WnVpa254S2hvcWl2LTI5STRmREVxalliZWQ4d1p0Njk4bmZXQks4ZWM4ZFNmdXNuUk44bWVhYXZUTl9OdjVHQUZreUY0ZmZaenl1RlUxeF9kaXdEbkZjQnhYWkRvQkc5M2pWVEtvQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>youroregonnews.com</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>f50677898d33941fa427d743</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>987a69de482d8d13094bacef</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr"/>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
+      <c r="BD2" s="2" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="BC6" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD6" s="2" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BE6" s="2" t="inlineStr">
+      <c r="BE2" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF6" s="2" t="inlineStr">
+      <c r="BF2" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG6" s="2" t="inlineStr"/>
-      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BG2" s="2" t="inlineStr"/>
+      <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH6"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8340,7 +7840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8403,6 +7903,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8706,9 +8210,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8719,7 +8243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8769,134 +8293,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -8906,46 +8430,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -8954,12 +8512,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -8969,90 +8527,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9062,94 +8624,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -9157,89 +8719,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-08-21.xlsx
+++ b/news_daily/2026-08-21.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -1963,170 +1963,194 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>CLX</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Clorox</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-08-21T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Is Clorox Stock Worth Buying as GOJO Growth Meets Margin Pressure?</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.213</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORDA1M0V5STZJYnZjTzdCSVdPQkhvSS1qa0J5VThsVkFHbnNUaUdScFUtQmZLSkxJT0VSS2loLTZ1QVVaUjM4VkRqRjJicTk1b3BjeFBVZFE4QVE1bDZObTJZQm40Y2NyQW9XYXhNdnRRMXd1dUNJS05Yak5JdkVHS3BYdXVYNHFyMGtkM1doQ1dPclhQT1VZbTV6Zw?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>e2ed991f82ec4556a3b141a35e8fe27e</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>67227f019967c42a43b36773</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr">
+        <is>
+          <t>b3bfb07265a165d7e7332a07</t>
+        </is>
+      </c>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" s="2" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>0.213</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORDA1M0V5STZJYnZjTzdCSVdPQkhvSS1qa0J5VThsVkFHbnNUaUdScFUtQmZLSkxJT0VSS2loLTZ1QVVaUjM4VkRqRjJicTk1b3BjeFBVZFE4QVE1bDZObTJZQm40Y2NyQW9XYXhNdnRRMXd1dUNJS05Yak5JdkVHS3BYdXVYNHFyMGtkM1doQ1dPclhQT1VZbTV6Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="inlineStr"/>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>67227f019967c42a43b36773</t>
-        </is>
-      </c>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>b3bfb07265a165d7e7332a07</t>
-        </is>
-      </c>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr"/>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="4" t="inlineStr"/>
-      <c r="AZ8" s="4" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr">
+      <c r="AP8" s="2" t="inlineStr"/>
+      <c r="AQ8" s="2" t="inlineStr"/>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr"/>
+      <c r="AT8" s="2" t="inlineStr"/>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr"/>
+      <c r="AX8" s="2" t="inlineStr"/>
+      <c r="AY8" s="2" t="inlineStr"/>
+      <c r="AZ8" s="2" t="inlineStr"/>
+      <c r="BA8" s="2" t="inlineStr"/>
+      <c r="BB8" s="2" t="inlineStr">
         <is>
           <t>CLX</t>
         </is>
       </c>
-      <c r="BC8" s="4" t="inlineStr">
+      <c r="BC8" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="4" t="inlineStr"/>
-      <c r="BE8" s="4" t="inlineStr">
+      <c r="BD8" s="2" t="inlineStr"/>
+      <c r="BE8" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF8" s="4" t="inlineStr"/>
-      <c r="BG8" s="4" t="inlineStr">
+      <c r="BF8" s="2" t="inlineStr"/>
+      <c r="BG8" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH8" s="4" t="inlineStr"/>
-      <c r="BI8" s="4" t="inlineStr"/>
-      <c r="BJ8" s="4" t="inlineStr"/>
-      <c r="BK8" s="4" t="inlineStr"/>
-      <c r="BL8" s="4" t="inlineStr"/>
+      <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3625,13 +3649,17 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -3684,7 +3712,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="4" t="inlineStr"/>
+      <c r="AB17" s="4" t="inlineStr">
+        <is>
+          <t>f6bc4c73b5544a02af794b8f79028113</t>
+        </is>
+      </c>
       <c r="AC17" s="4" t="inlineStr">
         <is>
           <t>04b77261a89eccd254c6e97b</t>
@@ -3705,7 +3737,11 @@
       <c r="AL17" s="4" t="inlineStr"/>
       <c r="AM17" s="4" t="inlineStr"/>
       <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="inlineStr"/>
+      <c r="AO17" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="4" t="inlineStr"/>
       <c r="AQ17" s="4" t="inlineStr"/>
       <c r="AR17" s="4" t="inlineStr"/>
@@ -3743,8 +3779,16 @@
       <c r="BH17" s="4" t="inlineStr"/>
       <c r="BI17" s="4" t="inlineStr"/>
       <c r="BJ17" s="4" t="inlineStr"/>
-      <c r="BK17" s="4" t="inlineStr"/>
-      <c r="BL17" s="4" t="inlineStr"/>
+      <c r="BK17" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4107,13 +4151,17 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -4166,7 +4214,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB20" s="4" t="inlineStr"/>
+      <c r="AB20" s="4" t="inlineStr">
+        <is>
+          <t>c5c8cc0996bf4da49008f48e97d3f3df</t>
+        </is>
+      </c>
       <c r="AC20" s="4" t="inlineStr">
         <is>
           <t>cb7e61d4f6747c426ab2f6de</t>
@@ -4187,7 +4239,11 @@
       <c r="AL20" s="4" t="inlineStr"/>
       <c r="AM20" s="4" t="inlineStr"/>
       <c r="AN20" s="4" t="inlineStr"/>
-      <c r="AO20" s="4" t="inlineStr"/>
+      <c r="AO20" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="4" t="inlineStr"/>
       <c r="AQ20" s="4" t="inlineStr"/>
       <c r="AR20" s="4" t="inlineStr"/>
@@ -4233,8 +4289,16 @@
       <c r="BH20" s="4" t="inlineStr"/>
       <c r="BI20" s="4" t="inlineStr"/>
       <c r="BJ20" s="4" t="inlineStr"/>
-      <c r="BK20" s="4" t="inlineStr"/>
-      <c r="BL20" s="4" t="inlineStr"/>
+      <c r="BK20" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4650,32 +4714,32 @@
       <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4715,7 +4779,7 @@
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -4728,7 +4792,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>84131343d2cf48a1b8baef1456ad5592</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
           <t>f50677898d33941fa427d743</t>
@@ -4751,7 +4819,7 @@
       <c r="AN23" s="2" t="inlineStr"/>
       <c r="AO23" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP23" s="2" t="inlineStr"/>
@@ -4793,10 +4861,22 @@
       </c>
       <c r="BG23" s="2" t="inlineStr"/>
       <c r="BH23" s="2" t="inlineStr"/>
-      <c r="BI23" s="2" t="inlineStr"/>
+      <c r="BI23" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ23" s="2" t="inlineStr"/>
-      <c r="BK23" s="2" t="inlineStr"/>
-      <c r="BL23" s="2" t="inlineStr"/>
+      <c r="BK23" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5000,7 +5080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL11"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5780,170 +5860,194 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Clorox</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Is Clorox Stock Worth Buying as GOJO Growth Meets Margin Pressure?</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Walt Disney Company (The)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21T10:55:17+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>美司法部反對就迪士尼ABC牌照訴訟案舉行緊急聽證會</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2624496</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>訴訟</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>7a286744031f4dfb8060d957459d14f1</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>153c67f9d747a4285d681ba3</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>3659fbbaa3cea9a8a2d4b980</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>0.213</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxORDA1M0V5STZJYnZjTzdCSVdPQkhvSS1qa0J5VThsVkFHbnNUaUdScFUtQmZLSkxJT0VSS2loLTZ1QVVaUjM4VkRqRjJicTk1b3BjeFBVZFE4QVE1bDZObTJZQm40Y2NyQW9XYXhNdnRRMXd1dUNJS05Yak5JdkVHS3BYdXVYNHFyMGtkM1doQ1dPclhQT1VZbTV6Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>67227f019967c42a43b36773</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>b3bfb07265a165d7e7332a07</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr"/>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>CLX</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr"/>
-      <c r="BG4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH4" s="4" t="inlineStr"/>
-      <c r="BI4" s="4" t="inlineStr"/>
-      <c r="BJ4" s="4" t="inlineStr"/>
-      <c r="BK4" s="4" t="inlineStr"/>
-      <c r="BL4" s="4" t="inlineStr"/>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr"/>
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="BC4" s="3" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD4" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="BE4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG4" s="3" t="inlineStr"/>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5958,22 +6062,22 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Walt Disney Company (The)</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21T10:55:17+08:00</t>
+          <t>2026-08-21T09:51:53+08:00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>美司法部反對就迪士尼ABC牌照訴訟案舉行緊急聽證會</t>
+          <t>雅培將支付6.7億美元以了結部分早產兒配方奶粉訴訟</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -6024,7 +6128,7 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>https://www.gelonghui.com/live/2624496</t>
+          <t>https://www.gelonghui.com/live/2624374</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
@@ -6051,17 +6155,17 @@
       <c r="AA5" s="3" t="inlineStr"/>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>7a286744031f4dfb8060d957459d14f1</t>
+          <t>9e313718274e4982b87c9e28823cbfe4</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>153c67f9d747a4285d681ba3</t>
+          <t>dbea804fa21928a28a097664</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>3659fbbaa3cea9a8a2d4b980</t>
+          <t>2c47dcd5fe84634ff135980b</t>
         </is>
       </c>
       <c r="AE5" s="3" t="inlineStr"/>
@@ -6093,7 +6197,7 @@
       <c r="BA5" s="3" t="inlineStr"/>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="BC5" s="3" t="inlineStr">
@@ -6103,17 +6207,17 @@
       </c>
       <c r="BD5" s="3" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="BE5" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
         </is>
       </c>
       <c r="BF5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="BG5" s="3" t="inlineStr"/>
@@ -6136,192 +6240,192 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Abbott Laboratories</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21T09:51:53+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>雅培將支付6.7億美元以了結部分早產兒配方奶粉訴訟</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>APO</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Apollo Global Management</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21T04:19:45+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Apollo Global Management Data Breach Impacts SSNs; Lawsuit Possible</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2624374</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>訴訟</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr">
-        <is>
-          <t>9e313718274e4982b87c9e28823cbfe4</t>
-        </is>
-      </c>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>dbea804fa21928a28a097664</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>2c47dcd5fe84634ff135980b</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>'-0.933</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNSGlaMkhFZWFObEtxVWo4MFdxSTBkZFJJWFU3Z3BKamRKa0VqRVBmWV9LY29pSy1YV29icjJwLWppRnVXZEMtMUFabGpRX2NYMGNBeHpvdDBDdFZZa2ZxY1dyaGFqcklCeUx2T09TcUFXWVVEUUltdGhBeDNlSzUteEtBMjFndVgxRllaZkhR?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>classaction.org</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>f6bc4c73b5544a02af794b8f79028113</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>04b77261a89eccd254c6e97b</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>95def5878b484fab12e3ab5e</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr"/>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD6" s="3" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG6" s="3" t="inlineStr"/>
-      <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr"/>
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>APO</t>
+        </is>
+      </c>
+      <c r="BC6" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr"/>
+      <c r="BG6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
         </is>
       </c>
     </row>
@@ -6338,22 +6442,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Apollo Global Management</t>
+          <t>Tyson Foods, Inc. Common Stock</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T04:19:45+08:00</t>
+          <t>2026-08-21T01:31:00+08:00</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Apollo Global Management Data Breach Impacts SSNs; Lawsuit Possible</t>
+          <t>Tyson Foods WARN Act Investigation: Joslin Plant Layoffs and Legal Scrutiny - News and Statistics</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
@@ -6364,7 +6468,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>資料外洩</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -6374,13 +6478,17 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -6390,7 +6498,7 @@
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>'-0.933</t>
+          <t>'-0.792</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr"/>
@@ -6404,28 +6512,28 @@
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxNSGlaMkhFZWFObEtxVWo4MFdxSTBkZFJJWFU3Z3BKamRKa0VqRVBmWV9LY29pSy1YV29icjJwLWppRnVXZEMtMUFabGpRX2NYMGNBeHpvdDBDdFZZa2ZxY1dyaGFqcklCeUx2T09TcUFXWVVEUUltdGhBeDNlSzUteEtBMjFndVgxRllaZkhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNa01QZE1lcWZ3XzJjYkMtU1BuUDdBVi1KRkpGbWhpNzZIRmd4UjRFdWFucjRhdTkxcUc4WU91bDlwVjV3YkJGaUFSeUxnbTE5dVg4Tnh0LUU5TUFXNFIzLWdVM3ZoMEV6MUVvX29Lem9lVmNMUHJjNUdoZ3dlUFNsbGN5MGVtNU95WGtSdjF1cHdtZVNxRHgzT0NzbTk?oc=5</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
         <is>
-          <t>classaction.org</t>
+          <t>indexbox.io</t>
         </is>
       </c>
       <c r="W7" s="4" t="inlineStr"/>
       <c r="X7" s="4" t="inlineStr">
         <is>
-          <t>CYBER</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>DATA_BREACH</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z7" s="4" t="inlineStr">
         <is>
-          <t>data breach</t>
+          <t>layoff；layoffs</t>
         </is>
       </c>
       <c r="AA7" s="4" t="inlineStr">
@@ -6433,15 +6541,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr"/>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>c5c8cc0996bf4da49008f48e97d3f3df</t>
+        </is>
+      </c>
       <c r="AC7" s="4" t="inlineStr">
         <is>
-          <t>04b77261a89eccd254c6e97b</t>
+          <t>cb7e61d4f6747c426ab2f6de</t>
         </is>
       </c>
       <c r="AD7" s="4" t="inlineStr">
         <is>
-          <t>95def5878b484fab12e3ab5e</t>
+          <t>2b6bd383b14b865532023325</t>
         </is>
       </c>
       <c r="AE7" s="4" t="inlineStr"/>
@@ -6454,7 +6566,11 @@
       <c r="AL7" s="4" t="inlineStr"/>
       <c r="AM7" s="4" t="inlineStr"/>
       <c r="AN7" s="4" t="inlineStr"/>
-      <c r="AO7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="4" t="inlineStr"/>
       <c r="AQ7" s="4" t="inlineStr"/>
       <c r="AR7" s="4" t="inlineStr"/>
@@ -6462,14 +6578,18 @@
       <c r="AT7" s="4" t="inlineStr"/>
       <c r="AU7" s="4" t="inlineStr"/>
       <c r="AV7" s="4" t="inlineStr"/>
-      <c r="AW7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
       <c r="AX7" s="4" t="inlineStr"/>
       <c r="AY7" s="4" t="inlineStr"/>
       <c r="AZ7" s="4" t="inlineStr"/>
       <c r="BA7" s="4" t="inlineStr"/>
       <c r="BB7" s="4" t="inlineStr">
         <is>
-          <t>APO</t>
+          <t>TSN</t>
         </is>
       </c>
       <c r="BC7" s="4" t="inlineStr">
@@ -6480,198 +6600,222 @@
       <c r="BD7" s="4" t="inlineStr"/>
       <c r="BE7" s="4" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="inlineStr"/>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
       <c r="BG7" s="4" t="inlineStr">
         <is>
-          <t>公司清單／交易所參照</t>
+          <t>交易所目前名單</t>
         </is>
       </c>
       <c r="BH7" s="4" t="inlineStr"/>
       <c r="BI7" s="4" t="inlineStr"/>
       <c r="BJ7" s="4" t="inlineStr"/>
-      <c r="BK7" s="4" t="inlineStr"/>
-      <c r="BL7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>TSN</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Tyson Foods, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-21T01:31:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Tyson Foods WARN Act Investigation: Joslin Plant Layoffs and Legal Scrutiny - News and Statistics</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:03:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>PNR Investor Alert: Pentair plc Securities Class Action Notice - Contact SueWallSt</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>'-0.082</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU2gyTWQ0ZnNBbHZ4N20waVVWNi1RZUsxMC1QNG9sT1FnelpqS0U1VkpHd1Y2bldEZlZ1YU1aSnBDUGFDZDc2ZS1SNUhYM1JhMkVNb3BHc1N3MFB5WFhIdTRYS0M1Y0hoeHVKLXg4d1RsZWVkSE90bkk2dTFXUnZHQzh5Q2N1Ym4zWjJIb2JzUlR1bG1VeHVudF9lbi1JaHRGdi12RnFIby1CeFB2WDVpVkhlZzdjZmRuUzJPSk5pc1JSS0dWSndmNXY0V2VjeTdELWxR?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>prnewswire.com</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>926ee65c0b0d4401ad96e40eb04c54e8</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>8aa08a7984611e910a09011d</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>784e9e349fa690e0b9d8c895</t>
+        </is>
+      </c>
+      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AF8" s="3" t="inlineStr"/>
+      <c r="AG8" s="3" t="inlineStr"/>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr"/>
+      <c r="AM8" s="3" t="inlineStr"/>
+      <c r="AN8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>'-0.792</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr"/>
-      <c r="R8" s="4" t="inlineStr"/>
-      <c r="S8" s="4" t="inlineStr"/>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNa01QZE1lcWZ3XzJjYkMtU1BuUDdBVi1KRkpGbWhpNzZIRmd4UjRFdWFucjRhdTkxcUc4WU91bDlwVjV3YkJGaUFSeUxnbTE5dVg4Tnh0LUU5TUFXNFIzLWdVM3ZoMEV6MUVvX29Lem9lVmNMUHJjNUdoZ3dlUFNsbGN5MGVtNU95WGtSdjF1cHdtZVNxRHgzT0NzbTk?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>indexbox.io</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr"/>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="4" t="inlineStr"/>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>cb7e61d4f6747c426ab2f6de</t>
-        </is>
-      </c>
-      <c r="AD8" s="4" t="inlineStr">
-        <is>
-          <t>2b6bd383b14b865532023325</t>
-        </is>
-      </c>
-      <c r="AE8" s="4" t="inlineStr"/>
-      <c r="AF8" s="4" t="inlineStr"/>
-      <c r="AG8" s="4" t="inlineStr"/>
-      <c r="AH8" s="4" t="inlineStr"/>
-      <c r="AI8" s="4" t="inlineStr"/>
-      <c r="AJ8" s="4" t="inlineStr"/>
-      <c r="AK8" s="4" t="inlineStr"/>
-      <c r="AL8" s="4" t="inlineStr"/>
-      <c r="AM8" s="4" t="inlineStr"/>
-      <c r="AN8" s="4" t="inlineStr"/>
-      <c r="AO8" s="4" t="inlineStr"/>
-      <c r="AP8" s="4" t="inlineStr"/>
-      <c r="AQ8" s="4" t="inlineStr"/>
-      <c r="AR8" s="4" t="inlineStr"/>
-      <c r="AS8" s="4" t="inlineStr"/>
-      <c r="AT8" s="4" t="inlineStr"/>
-      <c r="AU8" s="4" t="inlineStr"/>
-      <c r="AV8" s="4" t="inlineStr"/>
-      <c r="AW8" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX8" s="4" t="inlineStr"/>
-      <c r="AY8" s="4" t="inlineStr"/>
-      <c r="AZ8" s="4" t="inlineStr"/>
-      <c r="BA8" s="4" t="inlineStr"/>
-      <c r="BB8" s="4" t="inlineStr">
-        <is>
-          <t>TSN</t>
-        </is>
-      </c>
-      <c r="BC8" s="4" t="inlineStr">
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr"/>
+      <c r="AS8" s="3" t="inlineStr"/>
+      <c r="AT8" s="3" t="inlineStr"/>
+      <c r="AU8" s="3" t="inlineStr"/>
+      <c r="AV8" s="3" t="inlineStr"/>
+      <c r="AW8" s="3" t="inlineStr"/>
+      <c r="AX8" s="3" t="inlineStr"/>
+      <c r="AY8" s="3" t="inlineStr"/>
+      <c r="AZ8" s="3" t="inlineStr"/>
+      <c r="BA8" s="3" t="inlineStr"/>
+      <c r="BB8" s="3" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC8" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD8" s="4" t="inlineStr"/>
-      <c r="BE8" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH8" s="4" t="inlineStr"/>
-      <c r="BI8" s="4" t="inlineStr"/>
-      <c r="BJ8" s="4" t="inlineStr"/>
-      <c r="BK8" s="4" t="inlineStr"/>
-      <c r="BL8" s="4" t="inlineStr"/>
+      <c r="BD8" s="3" t="inlineStr"/>
+      <c r="BE8" s="3" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF8" s="3" t="inlineStr"/>
+      <c r="BG8" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -6686,22 +6830,22 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>Walt Disney Company (The)</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21T01:03:00+08:00</t>
+          <t>2026-08-21T00:36:53+08:00</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>PNR Investor Alert: Pentair plc Securities Class Action Notice - Contact SueWallSt</t>
+          <t>美國司法部反對在迪士尼ABC執照訴訟案中立即舉行聽證會</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -6740,28 +6884,24 @@
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>'-0.082</t>
-        </is>
-      </c>
+      <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr"/>
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr"/>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>公司清單／別名核對</t>
+          <t>主體證據不足</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOU2gyTWQ0ZnNBbHZ4N20waVVWNi1RZUsxMC1QNG9sT1FnelpqS0U1VkpHd1Y2bldEZlZ1YU1aSnBDUGFDZDc2ZS1SNUhYM1JhMkVNb3BHc1N3MFB5WFhIdTRYS0M1Y0hoeHVKLXg4d1RsZWVkSE90bkk2dTFXUnZHQzh5Q2N1Ym4zWjJIb2JzUlR1bG1VeHVudF9lbi1JaHRGdi12RnFIby1CeFB2WDVpVkhlZzdjZmRuUzJPSk5pc1JSS0dWSndmNXY0V2VjeTdELWxR?oc=5</t>
+          <t>https://tw.tradingview.com/symbols/NYSE-DIS/news/</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t>prnewswire.com</t>
+          <t>TradingView</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr"/>
@@ -6777,7 +6917,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>class action</t>
+          <t>訴訟</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -6787,17 +6927,17 @@
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>926ee65c0b0d4401ad96e40eb04c54e8</t>
+          <t>3b037c4187df46bfa3bf8be5c20b95f5</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>8aa08a7984611e910a09011d</t>
+          <t>ccb1ebcf32716240912f85bd</t>
         </is>
       </c>
       <c r="AD9" s="3" t="inlineStr">
         <is>
-          <t>784e9e349fa690e0b9d8c895</t>
+          <t>c937b4988a142cad289af5a8</t>
         </is>
       </c>
       <c r="AE9" s="3" t="inlineStr"/>
@@ -6829,28 +6969,36 @@
       <c r="BA9" s="3" t="inlineStr"/>
       <c r="BB9" s="3" t="inlineStr">
         <is>
-          <t>PNR</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="BC9" s="3" t="inlineStr">
         <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD9" s="3" t="inlineStr"/>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="BD9" s="3" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
       <c r="BE9" s="3" t="inlineStr">
         <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF9" s="3" t="inlineStr"/>
-      <c r="BG9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG9" s="3" t="inlineStr"/>
       <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
       <c r="BJ9" s="3" t="inlineStr"/>
       <c r="BK9" s="3" t="inlineStr">
         <is>
@@ -6876,22 +7024,22 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Walt Disney Company (The)</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21T00:36:53+08:00</t>
+          <t>2026-08-21T00:00:00+08:00</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>美國司法部反對在迪士尼ABC執照訴訟案中立即舉行聽證會</t>
+          <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Pentair plc Investors to Act: Class Action Filed Alleging Investor Harm</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -6930,24 +7078,28 @@
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>'-0.724</t>
+        </is>
+      </c>
       <c r="P10" s="3" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr"/>
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr"/>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-DIS/news/</t>
+          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxQTGJNY0lvNl9HUGY1NWdDSWxZa3I4a04tMlJNcm02ZW1zVlR0MGY0bVZVdzYtUXBhQXlIVHZZcGI0SVVySW1pYjBpdnMxdkVHRC1sb21CdGxrVEN4M2RTVWJrcFpHdmxNNkJKWDhWVVZJanZOczhhcFNCSUhqQzd1MWlYZzBlOVg3TnduREZLSk5GVHIxajZxZjZtTTJfYzdBUHoxLWFpVjg3R2h3ZXZCVV9Qa3MtNXFVLVpaSlVYaTNXbHFaUUc2SUlFcmZtcUM2b05ZTmNxTVZCb3pZcUY5QlRxdXlTUzJhR3R6OEZzVnBZZDVua1hjTk10M0h0ODR1d3RVSTUxVG9XYkhYMGZJ?oc=5</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>GlobeNewswire</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr"/>
@@ -6963,7 +7115,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t>訴訟</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -6973,17 +7125,17 @@
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>3b037c4187df46bfa3bf8be5c20b95f5</t>
+          <t>74f8ba1ec0284aeba251ba7b53cf0c51</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>ccb1ebcf32716240912f85bd</t>
+          <t>37237c9b76e3a0aef2ac53db</t>
         </is>
       </c>
       <c r="AD10" s="3" t="inlineStr">
         <is>
-          <t>c937b4988a142cad289af5a8</t>
+          <t>c5cc7637cf9a5876b35c475c</t>
         </is>
       </c>
       <c r="AE10" s="3" t="inlineStr"/>
@@ -7015,36 +7167,28 @@
       <c r="BA10" s="3" t="inlineStr"/>
       <c r="BB10" s="3" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="BC10" s="3" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD10" s="3" t="inlineStr">
-        <is>
-          <t>DIS</t>
-        </is>
-      </c>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD10" s="3" t="inlineStr"/>
       <c r="BE10" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG10" s="3" t="inlineStr"/>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF10" s="3" t="inlineStr"/>
+      <c r="BG10" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
       <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
+      <c r="BI10" s="3" t="inlineStr"/>
       <c r="BJ10" s="3" t="inlineStr"/>
       <c r="BK10" s="3" t="inlineStr">
         <is>
@@ -7057,198 +7201,8 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-21T00:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Bronstein, Gewirtz &amp; Grossman LLC Urges Pentair plc Investors to Act: Class Action Filed Alleging Investor Harm</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>'-0.724</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijwJBVV95cUxQTGJNY0lvNl9HUGY1NWdDSWxZa3I4a04tMlJNcm02ZW1zVlR0MGY0bVZVdzYtUXBhQXlIVHZZcGI0SVVySW1pYjBpdnMxdkVHRC1sb21CdGxrVEN4M2RTVWJrcFpHdmxNNkJKWDhWVVZJanZOczhhcFNCSUhqQzd1MWlYZzBlOVg3TnduREZLSk5GVHIxajZxZjZtTTJfYzdBUHoxLWFpVjg3R2h3ZXZCVV9Qa3MtNXFVLVpaSlVYaTNXbHFaUUc2SUlFcmZtcUM2b05ZTmNxTVZCb3pZcUY5QlRxdXlTUzJhR3R6OEZzVnBZZDVua1hjTk10M0h0ODR1d3RVSTUxVG9XYkhYMGZJ?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>GlobeNewswire</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="inlineStr">
-        <is>
-          <t>74f8ba1ec0284aeba251ba7b53cf0c51</t>
-        </is>
-      </c>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>37237c9b76e3a0aef2ac53db</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>c5cc7637cf9a5876b35c475c</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr"/>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC11" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF11" s="3" t="inlineStr"/>
-      <c r="BG11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr"/>
-      <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL11"/>
+  <autoFilter ref="A1:BL10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7259,7 +7213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7650,186 +7604,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Robinhood Markets</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-21T00:02:39+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Mount Hood loses Level 1 evacuation as wildfire moves away</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.866</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPb1RvVkZ5MGZJQXVfaE5iSlJwX0hCT09zVlc0YkliWFNxYmFLM2tOUHN1ZThiTDJ3WnVpa254S2hvcWl2LTI5STRmREVxalliZWQ4d1p0Njk4bmZXQks4ZWM4ZFNmdXNuUk44bWVhYXZUTl9OdjVHQUZreUY0ZmZaenl1RlUxeF9kaXdEbkZjQnhYWkRvQkc5M2pWVEtvQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>youroregonnews.com</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>f50677898d33941fa427d743</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>987a69de482d8d13094bacef</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-21.xlsx
+++ b/news_daily/2026-08-21.xlsx
@@ -903,13 +903,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -958,7 +962,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>f54a1aef8beb41b197685d01b763c885</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>c0d4469b23ec5c44579f69c9</t>
@@ -979,7 +987,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1025,8 +1037,16 @@
       <c r="BH2" s="2" t="inlineStr"/>
       <c r="BI2" s="2" t="inlineStr"/>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1062,28 +1082,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1123,7 +1147,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1132,7 +1156,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>09fac4d8312c4a13abe9b6297500d82c</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>764ea28e96179cd0195766a3</t>
@@ -1153,7 +1181,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1197,10 +1229,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1449,13 +1493,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1504,7 +1552,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>89a45f8f8893473a955282d7d0c7c23b</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>fea3e67f6f2144dd2b126c3f</t>
@@ -1525,7 +1577,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1571,8 +1627,16 @@
       <c r="BH5" s="2" t="inlineStr"/>
       <c r="BI5" s="2" t="inlineStr"/>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -2186,28 +2250,32 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2247,7 +2315,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -2256,7 +2324,11 @@
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>9e8d47e2350e422e8a4e1dbcd7cd2c79</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>7ad45f49ad16db86640f8092</t>
@@ -2277,7 +2349,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2321,10 +2397,22 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2360,28 +2448,32 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2421,7 +2513,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -2430,7 +2522,11 @@
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>74a29033c7d741a19d0784524fff723b</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
           <t>5fab0ba5f97f807a135460f4</t>
@@ -2451,7 +2547,11 @@
       <c r="AL10" s="2" t="inlineStr"/>
       <c r="AM10" s="2" t="inlineStr"/>
       <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="2" t="inlineStr"/>
       <c r="AQ10" s="2" t="inlineStr"/>
       <c r="AR10" s="2" t="inlineStr"/>
@@ -2495,10 +2595,22 @@
         </is>
       </c>
       <c r="BH10" s="2" t="inlineStr"/>
-      <c r="BI10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2534,28 +2646,32 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2595,7 +2711,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -2604,7 +2720,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>09148d34bd924d1694d92344d3b8dbd4</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>d917f458bb4ce5ac3cef8a76</t>
@@ -2625,7 +2745,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2669,10 +2793,22 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2723,13 +2859,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2778,7 +2918,11 @@
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>56482c6ea1044ead9711a920dc52bb99</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>b464662c72d6b354c09c9109</t>
@@ -2799,7 +2943,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2845,8 +2993,16 @@
       <c r="BH12" s="2" t="inlineStr"/>
       <c r="BI12" s="2" t="inlineStr"/>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3456,28 +3612,32 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -3517,7 +3677,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -3530,7 +3690,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>a01e5a22e1754df09e0dc4b8f0bebbc4</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
           <t>c711e5561296ba533f42e976</t>
@@ -3551,7 +3715,11 @@
       <c r="AL16" s="2" t="inlineStr"/>
       <c r="AM16" s="2" t="inlineStr"/>
       <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP16" s="2" t="inlineStr"/>
       <c r="AQ16" s="2" t="inlineStr"/>
       <c r="AR16" s="2" t="inlineStr"/>
@@ -3595,10 +3763,22 @@
         </is>
       </c>
       <c r="BH16" s="2" t="inlineStr"/>
-      <c r="BI16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ16" s="2" t="inlineStr"/>
-      <c r="BK16" s="2" t="inlineStr"/>
-      <c r="BL16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">

--- a/news_daily/2026-08-21.xlsx
+++ b/news_daily/2026-08-21.xlsx
@@ -4002,10 +4002,14 @@
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>一般公司更新</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4018,7 +4022,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -4061,7 +4069,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -4074,7 +4082,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>5c9281676e0643a08a40f0eec108c9ad</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
           <t>d1b24b9caee90c9f68ecafc2</t>
@@ -4095,7 +4107,11 @@
       <c r="AL18" s="2" t="inlineStr"/>
       <c r="AM18" s="2" t="inlineStr"/>
       <c r="AN18" s="2" t="inlineStr"/>
-      <c r="AO18" s="2" t="inlineStr"/>
+      <c r="AO18" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="2" t="inlineStr"/>
       <c r="AQ18" s="2" t="inlineStr"/>
       <c r="AR18" s="2" t="inlineStr"/>
@@ -4119,10 +4135,22 @@
       <c r="BF18" s="2" t="inlineStr"/>
       <c r="BG18" s="2" t="inlineStr"/>
       <c r="BH18" s="2" t="inlineStr"/>
-      <c r="BI18" s="2" t="inlineStr"/>
+      <c r="BI18" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ18" s="2" t="inlineStr"/>
-      <c r="BK18" s="2" t="inlineStr"/>
-      <c r="BL18" s="2" t="inlineStr"/>
+      <c r="BK18" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4156,10 +4184,14 @@
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>一般公司更新</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4172,7 +4204,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -4215,7 +4251,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -4228,7 +4264,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>58ee36814484431897356a96f8eedaed</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
           <t>d1b24b9caee90c9f68ecafc2</t>
@@ -4249,7 +4289,11 @@
       <c r="AL19" s="2" t="inlineStr"/>
       <c r="AM19" s="2" t="inlineStr"/>
       <c r="AN19" s="2" t="inlineStr"/>
-      <c r="AO19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP19" s="2" t="inlineStr"/>
       <c r="AQ19" s="2" t="inlineStr"/>
       <c r="AR19" s="2" t="inlineStr"/>
@@ -4277,10 +4321,22 @@
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
-      <c r="BI19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ19" s="2" t="inlineStr"/>
-      <c r="BK19" s="2" t="inlineStr"/>
-      <c r="BL19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
